--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY218"/>
+  <dimension ref="A1:AY258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25447,6 +25447,4066 @@
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>131260454</v>
+      </c>
+      <c r="B219" t="n">
+        <v>79244</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>393966</v>
+      </c>
+      <c r="R219" t="n">
+        <v>6950847</v>
+      </c>
+      <c r="S219" t="n">
+        <v>10</v>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT219" t="inlineStr"/>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>131259806</v>
+      </c>
+      <c r="B220" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>SO Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>394106</v>
+      </c>
+      <c r="R220" t="n">
+        <v>6951186</v>
+      </c>
+      <c r="S220" t="n">
+        <v>10</v>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT220" t="inlineStr"/>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>131258518</v>
+      </c>
+      <c r="B221" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>S om Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>393763</v>
+      </c>
+      <c r="R221" t="n">
+        <v>6951214</v>
+      </c>
+      <c r="S221" t="n">
+        <v>10</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT221" t="inlineStr"/>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>131260119</v>
+      </c>
+      <c r="B222" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>393903</v>
+      </c>
+      <c r="R222" t="n">
+        <v>6950826</v>
+      </c>
+      <c r="S222" t="n">
+        <v>10</v>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>2 bild, gran</t>
+        </is>
+      </c>
+      <c r="AD222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT222" t="inlineStr"/>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>131259983</v>
+      </c>
+      <c r="B223" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>SO Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>394187</v>
+      </c>
+      <c r="R223" t="n">
+        <v>6951218</v>
+      </c>
+      <c r="S223" t="n">
+        <v>10</v>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT223" t="inlineStr"/>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>131257750</v>
+      </c>
+      <c r="B224" t="n">
+        <v>83224</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>S om Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>393518</v>
+      </c>
+      <c r="R224" t="n">
+        <v>6951114</v>
+      </c>
+      <c r="S224" t="n">
+        <v>10</v>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT224" t="inlineStr"/>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>131257777</v>
+      </c>
+      <c r="B225" t="n">
+        <v>91829</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>S om Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>393537</v>
+      </c>
+      <c r="R225" t="n">
+        <v>6951131</v>
+      </c>
+      <c r="S225" t="n">
+        <v>10</v>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT225" t="inlineStr"/>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>131259760</v>
+      </c>
+      <c r="B226" t="n">
+        <v>83224</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>SO Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>394099</v>
+      </c>
+      <c r="R226" t="n">
+        <v>6951193</v>
+      </c>
+      <c r="S226" t="n">
+        <v>10</v>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT226" t="inlineStr"/>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>131260234</v>
+      </c>
+      <c r="B227" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>S om Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>394049</v>
+      </c>
+      <c r="R227" t="n">
+        <v>6951150</v>
+      </c>
+      <c r="S227" t="n">
+        <v>10</v>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT227" t="inlineStr"/>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>131259701</v>
+      </c>
+      <c r="B228" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>SO Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>394058</v>
+      </c>
+      <c r="R228" t="n">
+        <v>6951183</v>
+      </c>
+      <c r="S228" t="n">
+        <v>10</v>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT228" t="inlineStr"/>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>131259451</v>
+      </c>
+      <c r="B229" t="n">
+        <v>91829</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>S om Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>393972</v>
+      </c>
+      <c r="R229" t="n">
+        <v>6951237</v>
+      </c>
+      <c r="S229" t="n">
+        <v>10</v>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT229" t="inlineStr"/>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>131257647</v>
+      </c>
+      <c r="B230" t="n">
+        <v>83224</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>S om Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>393444</v>
+      </c>
+      <c r="R230" t="n">
+        <v>6951119</v>
+      </c>
+      <c r="S230" t="n">
+        <v>10</v>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT230" t="inlineStr"/>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>131258105</v>
+      </c>
+      <c r="B231" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>S om Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>393564</v>
+      </c>
+      <c r="R231" t="n">
+        <v>6950996</v>
+      </c>
+      <c r="S231" t="n">
+        <v>10</v>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT231" t="inlineStr"/>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>131258863</v>
+      </c>
+      <c r="B232" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>393928</v>
+      </c>
+      <c r="R232" t="n">
+        <v>6951139</v>
+      </c>
+      <c r="S232" t="n">
+        <v>10</v>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>1 bild, gran</t>
+        </is>
+      </c>
+      <c r="AD232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT232" t="inlineStr"/>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>131258813</v>
+      </c>
+      <c r="B233" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>S om Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>393900</v>
+      </c>
+      <c r="R233" t="n">
+        <v>6951166</v>
+      </c>
+      <c r="S233" t="n">
+        <v>10</v>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT233" t="inlineStr"/>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>131257896</v>
+      </c>
+      <c r="B234" t="n">
+        <v>91829</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>393554</v>
+      </c>
+      <c r="R234" t="n">
+        <v>6951144</v>
+      </c>
+      <c r="S234" t="n">
+        <v>10</v>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT234" t="inlineStr"/>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>131258822</v>
+      </c>
+      <c r="B235" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q235" t="n">
+        <v>393926</v>
+      </c>
+      <c r="R235" t="n">
+        <v>6951116</v>
+      </c>
+      <c r="S235" t="n">
+        <v>10</v>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>1 bild, gran</t>
+        </is>
+      </c>
+      <c r="AD235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT235" t="inlineStr"/>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>131260370</v>
+      </c>
+      <c r="B236" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q236" t="n">
+        <v>394001</v>
+      </c>
+      <c r="R236" t="n">
+        <v>6950899</v>
+      </c>
+      <c r="S236" t="n">
+        <v>10</v>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>2 bild, tall, rikligt</t>
+        </is>
+      </c>
+      <c r="AD236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT236" t="inlineStr"/>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>131260664</v>
+      </c>
+      <c r="B237" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q237" t="n">
+        <v>393848</v>
+      </c>
+      <c r="R237" t="n">
+        <v>6950708</v>
+      </c>
+      <c r="S237" t="n">
+        <v>10</v>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>1 bild, tydliga hackhål</t>
+        </is>
+      </c>
+      <c r="AD237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT237" t="inlineStr"/>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>131260485</v>
+      </c>
+      <c r="B238" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>393966</v>
+      </c>
+      <c r="R238" t="n">
+        <v>6950847</v>
+      </c>
+      <c r="S238" t="n">
+        <v>10</v>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>2 bild, högstubbe</t>
+        </is>
+      </c>
+      <c r="AD238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT238" t="inlineStr"/>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>131259721</v>
+      </c>
+      <c r="B239" t="n">
+        <v>91829</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>SO Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>394066</v>
+      </c>
+      <c r="R239" t="n">
+        <v>6951169</v>
+      </c>
+      <c r="S239" t="n">
+        <v>10</v>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT239" t="inlineStr"/>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>131258260</v>
+      </c>
+      <c r="B240" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q240" t="n">
+        <v>393671</v>
+      </c>
+      <c r="R240" t="n">
+        <v>6951134</v>
+      </c>
+      <c r="S240" t="n">
+        <v>10</v>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>1 bild på tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="AD240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT240" t="inlineStr"/>
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX240" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>131260181</v>
+      </c>
+      <c r="B241" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>SO Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q241" t="n">
+        <v>394066</v>
+      </c>
+      <c r="R241" t="n">
+        <v>6951169</v>
+      </c>
+      <c r="S241" t="n">
+        <v>10</v>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT241" t="inlineStr"/>
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX241" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>131259617</v>
+      </c>
+      <c r="B242" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q242" t="n">
+        <v>393858</v>
+      </c>
+      <c r="R242" t="n">
+        <v>6951054</v>
+      </c>
+      <c r="S242" t="n">
+        <v>10</v>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>2 bild, gran</t>
+        </is>
+      </c>
+      <c r="AD242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT242" t="inlineStr"/>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>131258022</v>
+      </c>
+      <c r="B243" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q243" t="n">
+        <v>393593</v>
+      </c>
+      <c r="R243" t="n">
+        <v>6951100</v>
+      </c>
+      <c r="S243" t="n">
+        <v>10</v>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>2 bild, gran</t>
+        </is>
+      </c>
+      <c r="AD243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT243" t="inlineStr"/>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>131257765</v>
+      </c>
+      <c r="B244" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q244" t="n">
+        <v>393501</v>
+      </c>
+      <c r="R244" t="n">
+        <v>6951126</v>
+      </c>
+      <c r="S244" t="n">
+        <v>10</v>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>1 bild, björk!</t>
+        </is>
+      </c>
+      <c r="AD244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT244" t="inlineStr"/>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>131260677</v>
+      </c>
+      <c r="B245" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q245" t="n">
+        <v>393848</v>
+      </c>
+      <c r="R245" t="n">
+        <v>6950708</v>
+      </c>
+      <c r="S245" t="n">
+        <v>10</v>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>1 bild, vid spår spillkråka</t>
+        </is>
+      </c>
+      <c r="AD245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT245" t="inlineStr"/>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>131257698</v>
+      </c>
+      <c r="B246" t="n">
+        <v>79244</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr"/>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q246" t="n">
+        <v>393501</v>
+      </c>
+      <c r="R246" t="n">
+        <v>6951126</v>
+      </c>
+      <c r="S246" t="n">
+        <v>10</v>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT246" t="inlineStr"/>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>131258127</v>
+      </c>
+      <c r="B247" t="n">
+        <v>91829</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>S om Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q247" t="n">
+        <v>393574</v>
+      </c>
+      <c r="R247" t="n">
+        <v>6950991</v>
+      </c>
+      <c r="S247" t="n">
+        <v>10</v>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT247" t="inlineStr"/>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>131260680</v>
+      </c>
+      <c r="B248" t="n">
+        <v>79244</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr"/>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q248" t="n">
+        <v>393848</v>
+      </c>
+      <c r="R248" t="n">
+        <v>6950708</v>
+      </c>
+      <c r="S248" t="n">
+        <v>10</v>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT248" t="inlineStr"/>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>131259937</v>
+      </c>
+      <c r="B249" t="n">
+        <v>83209</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>306</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Kornig nållav</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Chaenotheca chlorella</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr"/>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>SO Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q249" t="n">
+        <v>394158</v>
+      </c>
+      <c r="R249" t="n">
+        <v>6951255</v>
+      </c>
+      <c r="S249" t="n">
+        <v>10</v>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT249" t="inlineStr"/>
+      <c r="AW249" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX249" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>131259825</v>
+      </c>
+      <c r="B250" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q250" t="n">
+        <v>393904</v>
+      </c>
+      <c r="R250" t="n">
+        <v>6950987</v>
+      </c>
+      <c r="S250" t="n">
+        <v>10</v>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
+        </is>
+      </c>
+      <c r="AD250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT250" t="inlineStr"/>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>131257444</v>
+      </c>
+      <c r="B251" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>393426</v>
+      </c>
+      <c r="R251" t="n">
+        <v>6951191</v>
+      </c>
+      <c r="S251" t="n">
+        <v>10</v>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT251" t="inlineStr"/>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>131257828</v>
+      </c>
+      <c r="B252" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q252" t="n">
+        <v>393999</v>
+      </c>
+      <c r="R252" t="n">
+        <v>6951501</v>
+      </c>
+      <c r="S252" t="n">
+        <v>10</v>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>2 bild, gran lavskr</t>
+        </is>
+      </c>
+      <c r="AD252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT252" t="inlineStr"/>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>131258210</v>
+      </c>
+      <c r="B253" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>S om Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q253" t="n">
+        <v>393572</v>
+      </c>
+      <c r="R253" t="n">
+        <v>6951064</v>
+      </c>
+      <c r="S253" t="n">
+        <v>10</v>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT253" t="inlineStr"/>
+      <c r="AW253" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX253" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>131260600</v>
+      </c>
+      <c r="B254" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q254" t="n">
+        <v>393875</v>
+      </c>
+      <c r="R254" t="n">
+        <v>6950773</v>
+      </c>
+      <c r="S254" t="n">
+        <v>10</v>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
+        </is>
+      </c>
+      <c r="AD254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT254" t="inlineStr"/>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>131259944</v>
+      </c>
+      <c r="B255" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>SO Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q255" t="n">
+        <v>394171</v>
+      </c>
+      <c r="R255" t="n">
+        <v>6951274</v>
+      </c>
+      <c r="S255" t="n">
+        <v>10</v>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT255" t="inlineStr"/>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>131260113</v>
+      </c>
+      <c r="B256" t="n">
+        <v>79244</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr"/>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>SO Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>394112</v>
+      </c>
+      <c r="R256" t="n">
+        <v>6951132</v>
+      </c>
+      <c r="S256" t="n">
+        <v>10</v>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT256" t="inlineStr"/>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>131259465</v>
+      </c>
+      <c r="B257" t="n">
+        <v>79244</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr"/>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>S om Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>393972</v>
+      </c>
+      <c r="R257" t="n">
+        <v>6951237</v>
+      </c>
+      <c r="S257" t="n">
+        <v>10</v>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT257" t="inlineStr"/>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>131259470</v>
+      </c>
+      <c r="B258" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>S om Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>393972</v>
+      </c>
+      <c r="R258" t="n">
+        <v>6951237</v>
+      </c>
+      <c r="S258" t="n">
+        <v>10</v>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -25546,7 +25546,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>131259806</v>
+        <v>131258518</v>
       </c>
       <c r="B220" t="n">
         <v>57884</v>
@@ -25577,19 +25577,19 @@
       <c r="I220" t="inlineStr"/>
       <c r="M220" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>394106</v>
+        <v>393763</v>
       </c>
       <c r="R220" t="n">
-        <v>6951186</v>
+        <v>6951214</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25648,7 +25648,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>131258518</v>
+        <v>131259806</v>
       </c>
       <c r="B221" t="n">
         <v>57884</v>
@@ -25679,19 +25679,19 @@
       <c r="I221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>393763</v>
+        <v>394106</v>
       </c>
       <c r="R221" t="n">
-        <v>6951214</v>
+        <v>6951186</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25750,7 +25750,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>131260119</v>
+        <v>131259983</v>
       </c>
       <c r="B222" t="n">
         <v>57884</v>
@@ -25786,14 +25786,14 @@
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>393903</v>
+        <v>394187</v>
       </c>
       <c r="R222" t="n">
-        <v>6950826</v>
+        <v>6951218</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25828,11 +25828,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>2 bild, gran</t>
-        </is>
-      </c>
       <c r="AD222" t="b">
         <v>0</v>
       </c>
@@ -25845,19 +25840,19 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>131259983</v>
+        <v>131260119</v>
       </c>
       <c r="B223" t="n">
         <v>57884</v>
@@ -25893,14 +25888,14 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>394187</v>
+        <v>393903</v>
       </c>
       <c r="R223" t="n">
-        <v>6951218</v>
+        <v>6950826</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25935,6 +25930,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>2 bild, gran</t>
+        </is>
+      </c>
       <c r="AD223" t="b">
         <v>0</v>
       </c>
@@ -25947,12 +25947,12 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
@@ -26149,10 +26149,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>131259760</v>
+        <v>131260234</v>
       </c>
       <c r="B226" t="n">
-        <v>83224</v>
+        <v>57884</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26160,34 +26160,39 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>394099</v>
+        <v>394049</v>
       </c>
       <c r="R226" t="n">
-        <v>6951193</v>
+        <v>6951150</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26246,10 +26251,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>131260234</v>
+        <v>131259760</v>
       </c>
       <c r="B227" t="n">
-        <v>57884</v>
+        <v>83224</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26257,39 +26262,34 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>394049</v>
+        <v>394099</v>
       </c>
       <c r="R227" t="n">
-        <v>6951150</v>
+        <v>6951193</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26348,10 +26348,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>131259701</v>
+        <v>131257647</v>
       </c>
       <c r="B228" t="n">
-        <v>57884</v>
+        <v>83224</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26359,39 +26359,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>394058</v>
+        <v>393444</v>
       </c>
       <c r="R228" t="n">
-        <v>6951183</v>
+        <v>6951119</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26543,10 +26538,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>131257647</v>
+        <v>131258863</v>
       </c>
       <c r="B230" t="n">
-        <v>83224</v>
+        <v>57884</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26554,34 +26549,39 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>393444</v>
+        <v>393928</v>
       </c>
       <c r="R230" t="n">
-        <v>6951119</v>
+        <v>6951139</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26616,6 +26616,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>1 bild, gran</t>
+        </is>
+      </c>
       <c r="AD230" t="b">
         <v>0</v>
       </c>
@@ -26628,19 +26633,19 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>131258105</v>
+        <v>131259701</v>
       </c>
       <c r="B231" t="n">
         <v>57884</v>
@@ -26676,14 +26681,14 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>393564</v>
+        <v>394058</v>
       </c>
       <c r="R231" t="n">
-        <v>6950996</v>
+        <v>6951183</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26742,7 +26747,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>131258863</v>
+        <v>131258105</v>
       </c>
       <c r="B232" t="n">
         <v>57884</v>
@@ -26778,14 +26783,14 @@
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>393928</v>
+        <v>393564</v>
       </c>
       <c r="R232" t="n">
-        <v>6951139</v>
+        <v>6950996</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26820,11 +26825,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>1 bild, gran</t>
-        </is>
-      </c>
       <c r="AD232" t="b">
         <v>0</v>
       </c>
@@ -26837,12 +26837,12 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
@@ -26951,10 +26951,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>131257896</v>
+        <v>131260664</v>
       </c>
       <c r="B234" t="n">
-        <v>91829</v>
+        <v>57881</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26962,30 +26962,39 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P234" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>393554</v>
+        <v>393848</v>
       </c>
       <c r="R234" t="n">
-        <v>6951144</v>
+        <v>6950708</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27020,6 +27029,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>1 bild, tydliga hackhål</t>
+        </is>
+      </c>
       <c r="AD234" t="b">
         <v>0</v>
       </c>
@@ -27037,7 +27051,7 @@
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
@@ -27258,10 +27272,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>131260664</v>
+        <v>131257896</v>
       </c>
       <c r="B237" t="n">
-        <v>57881</v>
+        <v>91829</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27269,39 +27283,30 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>393848</v>
+        <v>393554</v>
       </c>
       <c r="R237" t="n">
-        <v>6950708</v>
+        <v>6951144</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27336,11 +27341,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>1 bild, tydliga hackhål</t>
-        </is>
-      </c>
       <c r="AD237" t="b">
         <v>0</v>
       </c>
@@ -27358,7 +27358,7 @@
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
@@ -27472,10 +27472,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>131259721</v>
+        <v>131258260</v>
       </c>
       <c r="B239" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27483,30 +27483,39 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>394066</v>
+        <v>393671</v>
       </c>
       <c r="R239" t="n">
-        <v>6951169</v>
+        <v>6951134</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27541,6 +27550,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>1 bild på tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD239" t="b">
         <v>0</v>
       </c>
@@ -27553,22 +27567,22 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>131258260</v>
+        <v>131259721</v>
       </c>
       <c r="B240" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27576,39 +27590,30 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>393671</v>
+        <v>394066</v>
       </c>
       <c r="R240" t="n">
-        <v>6951134</v>
+        <v>6951169</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27643,11 +27648,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC240" t="inlineStr">
-        <is>
-          <t>1 bild på tretåig hackspett</t>
-        </is>
-      </c>
       <c r="AD240" t="b">
         <v>0</v>
       </c>
@@ -27660,19 +27660,19 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>131260181</v>
+        <v>131259617</v>
       </c>
       <c r="B241" t="n">
         <v>57884</v>
@@ -27708,14 +27708,14 @@
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>394066</v>
+        <v>393858</v>
       </c>
       <c r="R241" t="n">
-        <v>6951169</v>
+        <v>6951054</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27750,6 +27750,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>2 bild, gran</t>
+        </is>
+      </c>
       <c r="AD241" t="b">
         <v>0</v>
       </c>
@@ -27762,19 +27767,19 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>131259617</v>
+        <v>131258022</v>
       </c>
       <c r="B242" t="n">
         <v>57884</v>
@@ -27814,10 +27819,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>393858</v>
+        <v>393593</v>
       </c>
       <c r="R242" t="n">
-        <v>6951054</v>
+        <v>6951100</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27881,7 +27886,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>131258022</v>
+        <v>131260181</v>
       </c>
       <c r="B243" t="n">
         <v>57884</v>
@@ -27917,14 +27922,14 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>393593</v>
+        <v>394066</v>
       </c>
       <c r="R243" t="n">
-        <v>6951100</v>
+        <v>6951169</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27959,11 +27964,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>2 bild, gran</t>
-        </is>
-      </c>
       <c r="AD243" t="b">
         <v>0</v>
       </c>
@@ -27976,12 +27976,12 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
@@ -28202,45 +28202,45 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>131257698</v>
+        <v>131259937</v>
       </c>
       <c r="B246" t="n">
-        <v>79244</v>
+        <v>83209</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>393501</v>
+        <v>394158</v>
       </c>
       <c r="R246" t="n">
-        <v>6951126</v>
+        <v>6951255</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28287,22 +28287,22 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>131258127</v>
+        <v>131257698</v>
       </c>
       <c r="B247" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28310,30 +28310,34 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>393574</v>
+        <v>393501</v>
       </c>
       <c r="R247" t="n">
-        <v>6950991</v>
+        <v>6951126</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28380,12 +28384,12 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
@@ -28489,45 +28493,41 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>131259937</v>
+        <v>131258127</v>
       </c>
       <c r="B249" t="n">
-        <v>83209</v>
+        <v>91829</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>306</v>
+        <v>5432</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>394158</v>
+        <v>393574</v>
       </c>
       <c r="R249" t="n">
-        <v>6951255</v>
+        <v>6950991</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -29310,10 +29310,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>131259465</v>
+        <v>131259470</v>
       </c>
       <c r="B257" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -29321,24 +29321,29 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P257" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
@@ -29407,10 +29412,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>131259470</v>
+        <v>131259465</v>
       </c>
       <c r="B258" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -29418,29 +29423,24 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -25452,7 +25452,7 @@
         <v>131260454</v>
       </c>
       <c r="B219" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>131259983</v>
+        <v>131260119</v>
       </c>
       <c r="B222" t="n">
         <v>57884</v>
@@ -25786,14 +25786,14 @@
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>394187</v>
+        <v>393903</v>
       </c>
       <c r="R222" t="n">
-        <v>6951218</v>
+        <v>6950826</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25828,6 +25828,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>2 bild, gran</t>
+        </is>
+      </c>
       <c r="AD222" t="b">
         <v>0</v>
       </c>
@@ -25840,19 +25845,19 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>131260119</v>
+        <v>131259983</v>
       </c>
       <c r="B223" t="n">
         <v>57884</v>
@@ -25888,14 +25893,14 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>393903</v>
+        <v>394187</v>
       </c>
       <c r="R223" t="n">
-        <v>6950826</v>
+        <v>6951218</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25930,11 +25935,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>2 bild, gran</t>
-        </is>
-      </c>
       <c r="AD223" t="b">
         <v>0</v>
       </c>
@@ -25947,12 +25947,12 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
@@ -25962,7 +25962,7 @@
         <v>131257750</v>
       </c>
       <c r="B224" t="n">
-        <v>83224</v>
+        <v>83225</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>131257777</v>
       </c>
       <c r="B225" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>131259760</v>
       </c>
       <c r="B227" t="n">
-        <v>83224</v>
+        <v>83225</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>131257647</v>
       </c>
       <c r="B228" t="n">
-        <v>83224</v>
+        <v>83225</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>131259451</v>
       </c>
       <c r="B229" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>131258863</v>
+        <v>131259701</v>
       </c>
       <c r="B230" t="n">
         <v>57884</v>
@@ -26574,14 +26574,14 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>393928</v>
+        <v>394058</v>
       </c>
       <c r="R230" t="n">
-        <v>6951139</v>
+        <v>6951183</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26616,11 +26616,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>1 bild, gran</t>
-        </is>
-      </c>
       <c r="AD230" t="b">
         <v>0</v>
       </c>
@@ -26633,19 +26628,19 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>131259701</v>
+        <v>131258105</v>
       </c>
       <c r="B231" t="n">
         <v>57884</v>
@@ -26681,14 +26676,14 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>394058</v>
+        <v>393564</v>
       </c>
       <c r="R231" t="n">
-        <v>6951183</v>
+        <v>6950996</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26747,7 +26742,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>131258105</v>
+        <v>131258863</v>
       </c>
       <c r="B232" t="n">
         <v>57884</v>
@@ -26783,14 +26778,14 @@
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>393564</v>
+        <v>393928</v>
       </c>
       <c r="R232" t="n">
-        <v>6950996</v>
+        <v>6951139</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26825,6 +26820,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>1 bild, gran</t>
+        </is>
+      </c>
       <c r="AD232" t="b">
         <v>0</v>
       </c>
@@ -26837,12 +26837,12 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
@@ -26951,10 +26951,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>131260664</v>
+        <v>131257896</v>
       </c>
       <c r="B234" t="n">
-        <v>57881</v>
+        <v>91830</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26962,39 +26962,30 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr"/>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P234" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>393848</v>
+        <v>393554</v>
       </c>
       <c r="R234" t="n">
-        <v>6950708</v>
+        <v>6951144</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27029,11 +27020,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>1 bild, tydliga hackhål</t>
-        </is>
-      </c>
       <c r="AD234" t="b">
         <v>0</v>
       </c>
@@ -27051,14 +27037,14 @@
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>131258822</v>
+        <v>131260370</v>
       </c>
       <c r="B235" t="n">
         <v>57884</v>
@@ -27089,7 +27075,7 @@
       <c r="I235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -27098,10 +27084,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>393926</v>
+        <v>394001</v>
       </c>
       <c r="R235" t="n">
-        <v>6951116</v>
+        <v>6950899</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27138,7 +27124,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>1 bild, gran</t>
+          <t>2 bild, tall, rikligt</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -27158,14 +27144,14 @@
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>131260370</v>
+        <v>131258822</v>
       </c>
       <c r="B236" t="n">
         <v>57884</v>
@@ -27196,7 +27182,7 @@
       <c r="I236" t="inlineStr"/>
       <c r="M236" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -27205,10 +27191,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>394001</v>
+        <v>393926</v>
       </c>
       <c r="R236" t="n">
-        <v>6950899</v>
+        <v>6951116</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27245,7 +27231,7 @@
       </c>
       <c r="AC236" t="inlineStr">
         <is>
-          <t>2 bild, tall, rikligt</t>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -27265,17 +27251,17 @@
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>131257896</v>
+        <v>131260664</v>
       </c>
       <c r="B237" t="n">
-        <v>91829</v>
+        <v>57881</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27283,30 +27269,39 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>393554</v>
+        <v>393848</v>
       </c>
       <c r="R237" t="n">
-        <v>6951144</v>
+        <v>6950708</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27341,6 +27336,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>1 bild, tydliga hackhål</t>
+        </is>
+      </c>
       <c r="AD237" t="b">
         <v>0</v>
       </c>
@@ -27358,7 +27358,7 @@
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
@@ -27472,10 +27472,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>131258260</v>
+        <v>131259721</v>
       </c>
       <c r="B239" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27483,39 +27483,30 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>393671</v>
+        <v>394066</v>
       </c>
       <c r="R239" t="n">
-        <v>6951134</v>
+        <v>6951169</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27550,11 +27541,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>1 bild på tretåig hackspett</t>
-        </is>
-      </c>
       <c r="AD239" t="b">
         <v>0</v>
       </c>
@@ -27567,22 +27553,22 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>131259721</v>
+        <v>131258260</v>
       </c>
       <c r="B240" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27590,30 +27576,39 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>394066</v>
+        <v>393671</v>
       </c>
       <c r="R240" t="n">
-        <v>6951169</v>
+        <v>6951134</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27648,6 +27643,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>1 bild på tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD240" t="b">
         <v>0</v>
       </c>
@@ -27660,19 +27660,19 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bjarne Tutturen, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>131259617</v>
+        <v>131260181</v>
       </c>
       <c r="B241" t="n">
         <v>57884</v>
@@ -27708,14 +27708,14 @@
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>393858</v>
+        <v>394066</v>
       </c>
       <c r="R241" t="n">
-        <v>6951054</v>
+        <v>6951169</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27750,11 +27750,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>2 bild, gran</t>
-        </is>
-      </c>
       <c r="AD241" t="b">
         <v>0</v>
       </c>
@@ -27767,12 +27762,12 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
@@ -27886,7 +27881,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>131260181</v>
+        <v>131259617</v>
       </c>
       <c r="B243" t="n">
         <v>57884</v>
@@ -27922,14 +27917,14 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>394066</v>
+        <v>393858</v>
       </c>
       <c r="R243" t="n">
-        <v>6951169</v>
+        <v>6951054</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27964,6 +27959,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>2 bild, gran</t>
+        </is>
+      </c>
       <c r="AD243" t="b">
         <v>0</v>
       </c>
@@ -27976,12 +27976,12 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
@@ -28202,45 +28202,45 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>131259937</v>
+        <v>131257698</v>
       </c>
       <c r="B246" t="n">
-        <v>83209</v>
+        <v>79245</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>394158</v>
+        <v>393501</v>
       </c>
       <c r="R246" t="n">
-        <v>6951255</v>
+        <v>6951126</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28287,22 +28287,22 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>131257698</v>
+        <v>131260680</v>
       </c>
       <c r="B247" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28334,10 +28334,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>393501</v>
+        <v>393848</v>
       </c>
       <c r="R247" t="n">
-        <v>6951126</v>
+        <v>6950708</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28389,17 +28389,17 @@
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>131260680</v>
+        <v>131258127</v>
       </c>
       <c r="B248" t="n">
-        <v>79244</v>
+        <v>91830</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28407,34 +28407,30 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>393848</v>
+        <v>393574</v>
       </c>
       <c r="R248" t="n">
-        <v>6950708</v>
+        <v>6950991</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28481,53 +28477,57 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>131258127</v>
+        <v>131259937</v>
       </c>
       <c r="B249" t="n">
-        <v>91829</v>
+        <v>83210</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5432</v>
+        <v>306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr"/>
+          <t>Chaenotheca chlorella</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>393574</v>
+        <v>394158</v>
       </c>
       <c r="R249" t="n">
-        <v>6950991</v>
+        <v>6951255</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28586,27 +28586,27 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>131259825</v>
+        <v>131257444</v>
       </c>
       <c r="B250" t="n">
-        <v>57884</v>
+        <v>57988</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -28617,7 +28617,7 @@
       <c r="I250" t="inlineStr"/>
       <c r="M250" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
@@ -28626,10 +28626,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>393904</v>
+        <v>393426</v>
       </c>
       <c r="R250" t="n">
-        <v>6950987</v>
+        <v>6951191</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28662,11 +28662,6 @@
       <c r="AA250" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28693,27 +28688,27 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>131257444</v>
+        <v>131259825</v>
       </c>
       <c r="B251" t="n">
-        <v>57988</v>
+        <v>57884</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -28724,7 +28719,7 @@
       <c r="I251" t="inlineStr"/>
       <c r="M251" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
@@ -28733,10 +28728,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>393426</v>
+        <v>393904</v>
       </c>
       <c r="R251" t="n">
-        <v>6951191</v>
+        <v>6950987</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28769,6 +28764,11 @@
       <c r="AA251" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -29216,7 +29216,7 @@
         <v>131260113</v>
       </c>
       <c r="B256" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29310,10 +29310,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>131259470</v>
+        <v>131259465</v>
       </c>
       <c r="B257" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -29321,29 +29321,24 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P257" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
@@ -29412,10 +29407,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>131259465</v>
+        <v>131259470</v>
       </c>
       <c r="B258" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -29423,24 +29418,29 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -25750,10 +25750,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>131260119</v>
+        <v>131257750</v>
       </c>
       <c r="B222" t="n">
-        <v>57884</v>
+        <v>83225</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25761,39 +25761,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>393903</v>
+        <v>393518</v>
       </c>
       <c r="R222" t="n">
-        <v>6950826</v>
+        <v>6951114</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25828,11 +25823,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>2 bild, gran</t>
-        </is>
-      </c>
       <c r="AD222" t="b">
         <v>0</v>
       </c>
@@ -25845,19 +25835,19 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>131259983</v>
+        <v>131260119</v>
       </c>
       <c r="B223" t="n">
         <v>57884</v>
@@ -25893,14 +25883,14 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>394187</v>
+        <v>393903</v>
       </c>
       <c r="R223" t="n">
-        <v>6951218</v>
+        <v>6950826</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25935,6 +25925,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>2 bild, gran</t>
+        </is>
+      </c>
       <c r="AD223" t="b">
         <v>0</v>
       </c>
@@ -25947,22 +25942,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>131257750</v>
+        <v>131259983</v>
       </c>
       <c r="B224" t="n">
-        <v>83225</v>
+        <v>57884</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25970,34 +25965,39 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>393518</v>
+        <v>394187</v>
       </c>
       <c r="R224" t="n">
-        <v>6951114</v>
+        <v>6951218</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26149,10 +26149,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>131260234</v>
+        <v>131259760</v>
       </c>
       <c r="B226" t="n">
-        <v>57884</v>
+        <v>83225</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26160,39 +26160,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>394049</v>
+        <v>394099</v>
       </c>
       <c r="R226" t="n">
-        <v>6951150</v>
+        <v>6951193</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26251,10 +26246,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>131259760</v>
+        <v>131260234</v>
       </c>
       <c r="B227" t="n">
-        <v>83225</v>
+        <v>57884</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26262,34 +26257,39 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>394099</v>
+        <v>394049</v>
       </c>
       <c r="R227" t="n">
-        <v>6951193</v>
+        <v>6951150</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -27044,10 +27044,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>131260370</v>
+        <v>131260664</v>
       </c>
       <c r="B235" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27055,16 +27055,16 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -27084,10 +27084,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>394001</v>
+        <v>393848</v>
       </c>
       <c r="R235" t="n">
-        <v>6950899</v>
+        <v>6950708</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27124,7 +27124,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>2 bild, tall, rikligt</t>
+          <t>1 bild, tydliga hackhål</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -27151,10 +27151,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>131258822</v>
+        <v>131260485</v>
       </c>
       <c r="B236" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27162,16 +27162,16 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -27182,7 +27182,7 @@
       <c r="I236" t="inlineStr"/>
       <c r="M236" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -27191,10 +27191,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>393926</v>
+        <v>393966</v>
       </c>
       <c r="R236" t="n">
-        <v>6951116</v>
+        <v>6950847</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="AC236" t="inlineStr">
         <is>
-          <t>1 bild, gran</t>
+          <t>2 bild, högstubbe</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -27251,17 +27251,17 @@
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>131260664</v>
+        <v>131260370</v>
       </c>
       <c r="B237" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27269,16 +27269,16 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -27298,10 +27298,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>393848</v>
+        <v>394001</v>
       </c>
       <c r="R237" t="n">
-        <v>6950708</v>
+        <v>6950899</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27338,7 +27338,7 @@
       </c>
       <c r="AC237" t="inlineStr">
         <is>
-          <t>1 bild, tydliga hackhål</t>
+          <t>2 bild, tall, rikligt</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -27365,10 +27365,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>131260485</v>
+        <v>131258822</v>
       </c>
       <c r="B238" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -27376,16 +27376,16 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -27396,7 +27396,7 @@
       <c r="I238" t="inlineStr"/>
       <c r="M238" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -27405,10 +27405,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>393966</v>
+        <v>393926</v>
       </c>
       <c r="R238" t="n">
-        <v>6950847</v>
+        <v>6951116</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27445,7 +27445,7 @@
       </c>
       <c r="AC238" t="inlineStr">
         <is>
-          <t>2 bild, högstubbe</t>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27465,17 +27465,17 @@
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>131259721</v>
+        <v>131258260</v>
       </c>
       <c r="B239" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27483,30 +27483,39 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>394066</v>
+        <v>393671</v>
       </c>
       <c r="R239" t="n">
-        <v>6951169</v>
+        <v>6951134</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27541,6 +27550,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>1 bild på tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD239" t="b">
         <v>0</v>
       </c>
@@ -27553,22 +27567,22 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bjarne Tutturen, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>131258260</v>
+        <v>131259721</v>
       </c>
       <c r="B240" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27576,39 +27590,30 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>393671</v>
+        <v>394066</v>
       </c>
       <c r="R240" t="n">
-        <v>6951134</v>
+        <v>6951169</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27643,11 +27648,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC240" t="inlineStr">
-        <is>
-          <t>1 bild på tretåig hackspett</t>
-        </is>
-      </c>
       <c r="AD240" t="b">
         <v>0</v>
       </c>
@@ -27660,12 +27660,12 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
@@ -28299,45 +28299,45 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>131260680</v>
+        <v>131259937</v>
       </c>
       <c r="B247" t="n">
-        <v>79245</v>
+        <v>83210</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>393848</v>
+        <v>394158</v>
       </c>
       <c r="R247" t="n">
-        <v>6950708</v>
+        <v>6951255</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28384,22 +28384,22 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>131258127</v>
+        <v>131260680</v>
       </c>
       <c r="B248" t="n">
-        <v>91830</v>
+        <v>79245</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28407,30 +28407,34 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>393574</v>
+        <v>393848</v>
       </c>
       <c r="R248" t="n">
-        <v>6950991</v>
+        <v>6950708</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28477,57 +28481,53 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>131259937</v>
+        <v>131258127</v>
       </c>
       <c r="B249" t="n">
-        <v>83210</v>
+        <v>91830</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>306</v>
+        <v>5432</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>394158</v>
+        <v>393574</v>
       </c>
       <c r="R249" t="n">
-        <v>6951255</v>
+        <v>6950991</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -27472,10 +27472,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>131258260</v>
+        <v>131259721</v>
       </c>
       <c r="B239" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27483,39 +27483,30 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>393671</v>
+        <v>394066</v>
       </c>
       <c r="R239" t="n">
-        <v>6951134</v>
+        <v>6951169</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27550,11 +27541,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>1 bild på tretåig hackspett</t>
-        </is>
-      </c>
       <c r="AD239" t="b">
         <v>0</v>
       </c>
@@ -27567,22 +27553,22 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>131259721</v>
+        <v>131258260</v>
       </c>
       <c r="B240" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27590,30 +27576,39 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>394066</v>
+        <v>393671</v>
       </c>
       <c r="R240" t="n">
-        <v>6951169</v>
+        <v>6951134</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27648,6 +27643,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>1 bild på tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD240" t="b">
         <v>0</v>
       </c>
@@ -27660,12 +27660,12 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bjarne Tutturen, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
@@ -28586,27 +28586,27 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>131257444</v>
+        <v>131259825</v>
       </c>
       <c r="B250" t="n">
-        <v>57988</v>
+        <v>57884</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -28617,7 +28617,7 @@
       <c r="I250" t="inlineStr"/>
       <c r="M250" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
@@ -28626,10 +28626,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>393426</v>
+        <v>393904</v>
       </c>
       <c r="R250" t="n">
-        <v>6951191</v>
+        <v>6950987</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28662,6 +28662,11 @@
       <c r="AA250" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28688,27 +28693,27 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>131259825</v>
+        <v>131257444</v>
       </c>
       <c r="B251" t="n">
-        <v>57884</v>
+        <v>57988</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -28719,7 +28724,7 @@
       <c r="I251" t="inlineStr"/>
       <c r="M251" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
@@ -28728,10 +28733,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>393904</v>
+        <v>393426</v>
       </c>
       <c r="R251" t="n">
-        <v>6950987</v>
+        <v>6951191</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28764,11 +28769,6 @@
       <c r="AA251" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD251" t="b">

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -25546,7 +25546,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>131258518</v>
+        <v>131259806</v>
       </c>
       <c r="B220" t="n">
         <v>57884</v>
@@ -25577,19 +25577,19 @@
       <c r="I220" t="inlineStr"/>
       <c r="M220" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>393763</v>
+        <v>394106</v>
       </c>
       <c r="R220" t="n">
-        <v>6951214</v>
+        <v>6951186</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25648,7 +25648,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>131259806</v>
+        <v>131258518</v>
       </c>
       <c r="B221" t="n">
         <v>57884</v>
@@ -25679,19 +25679,19 @@
       <c r="I221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>394106</v>
+        <v>393763</v>
       </c>
       <c r="R221" t="n">
-        <v>6951186</v>
+        <v>6951214</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25847,7 +25847,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>131260119</v>
+        <v>131259983</v>
       </c>
       <c r="B223" t="n">
         <v>57884</v>
@@ -25883,14 +25883,14 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>393903</v>
+        <v>394187</v>
       </c>
       <c r="R223" t="n">
-        <v>6950826</v>
+        <v>6951218</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25925,11 +25925,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>2 bild, gran</t>
-        </is>
-      </c>
       <c r="AD223" t="b">
         <v>0</v>
       </c>
@@ -25942,22 +25937,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>131259983</v>
+        <v>131257777</v>
       </c>
       <c r="B224" t="n">
-        <v>57884</v>
+        <v>91833</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25965,39 +25960,30 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>394187</v>
+        <v>393537</v>
       </c>
       <c r="R224" t="n">
-        <v>6951218</v>
+        <v>6951131</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26056,10 +26042,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>131257777</v>
+        <v>131259760</v>
       </c>
       <c r="B225" t="n">
-        <v>91830</v>
+        <v>83225</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26067,30 +26053,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>393537</v>
+        <v>394099</v>
       </c>
       <c r="R225" t="n">
-        <v>6951131</v>
+        <v>6951193</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26149,10 +26139,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>131259760</v>
+        <v>131260234</v>
       </c>
       <c r="B226" t="n">
-        <v>83225</v>
+        <v>57884</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26160,34 +26150,39 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>394099</v>
+        <v>394049</v>
       </c>
       <c r="R226" t="n">
-        <v>6951193</v>
+        <v>6951150</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26246,7 +26241,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>131260234</v>
+        <v>131259701</v>
       </c>
       <c r="B227" t="n">
         <v>57884</v>
@@ -26282,14 +26277,14 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>394049</v>
+        <v>394058</v>
       </c>
       <c r="R227" t="n">
-        <v>6951150</v>
+        <v>6951183</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26348,10 +26343,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>131257647</v>
+        <v>131259451</v>
       </c>
       <c r="B228" t="n">
-        <v>83225</v>
+        <v>91833</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26359,23 +26354,19 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
@@ -26383,10 +26374,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>393444</v>
+        <v>393972</v>
       </c>
       <c r="R228" t="n">
-        <v>6951119</v>
+        <v>6951237</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26445,10 +26436,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>131259451</v>
+        <v>131257647</v>
       </c>
       <c r="B229" t="n">
-        <v>91830</v>
+        <v>83225</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26456,19 +26447,23 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
@@ -26476,10 +26471,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>393972</v>
+        <v>393444</v>
       </c>
       <c r="R229" t="n">
-        <v>6951237</v>
+        <v>6951119</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26538,7 +26533,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>131259701</v>
+        <v>131258105</v>
       </c>
       <c r="B230" t="n">
         <v>57884</v>
@@ -26574,14 +26569,14 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>394058</v>
+        <v>393564</v>
       </c>
       <c r="R230" t="n">
-        <v>6951183</v>
+        <v>6950996</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26640,7 +26635,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>131258105</v>
+        <v>131258813</v>
       </c>
       <c r="B231" t="n">
         <v>57884</v>
@@ -26680,10 +26675,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>393564</v>
+        <v>393900</v>
       </c>
       <c r="R231" t="n">
-        <v>6950996</v>
+        <v>6951166</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26742,10 +26737,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>131258863</v>
+        <v>131259721</v>
       </c>
       <c r="B232" t="n">
-        <v>57884</v>
+        <v>91833</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26753,39 +26748,30 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr"/>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>393928</v>
+        <v>394066</v>
       </c>
       <c r="R232" t="n">
-        <v>6951139</v>
+        <v>6951169</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26820,11 +26806,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>1 bild, gran</t>
-        </is>
-      </c>
       <c r="AD232" t="b">
         <v>0</v>
       </c>
@@ -26837,19 +26818,19 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>131258813</v>
+        <v>131260181</v>
       </c>
       <c r="B233" t="n">
         <v>57884</v>
@@ -26885,14 +26866,14 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>393900</v>
+        <v>394066</v>
       </c>
       <c r="R233" t="n">
-        <v>6951166</v>
+        <v>6951169</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26951,10 +26932,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>131257896</v>
+        <v>131257765</v>
       </c>
       <c r="B234" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26962,30 +26943,39 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P234" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>393554</v>
+        <v>393501</v>
       </c>
       <c r="R234" t="n">
-        <v>6951144</v>
+        <v>6951126</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27018,6 +27008,11 @@
       <c r="AA234" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>1 bild, björk!</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -27044,50 +27039,45 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>131260664</v>
+        <v>131259937</v>
       </c>
       <c r="B235" t="n">
-        <v>57881</v>
+        <v>83210</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>100049</v>
+        <v>306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>393848</v>
+        <v>394158</v>
       </c>
       <c r="R235" t="n">
-        <v>6950708</v>
+        <v>6951255</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27122,11 +27112,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>1 bild, tydliga hackhål</t>
-        </is>
-      </c>
       <c r="AD235" t="b">
         <v>0</v>
       </c>
@@ -27139,22 +27124,22 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>131260485</v>
+        <v>131257698</v>
       </c>
       <c r="B236" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27162,39 +27147,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P236" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>393966</v>
+        <v>393501</v>
       </c>
       <c r="R236" t="n">
-        <v>6950847</v>
+        <v>6951126</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27229,11 +27209,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>2 bild, högstubbe</t>
-        </is>
-      </c>
       <c r="AD236" t="b">
         <v>0</v>
       </c>
@@ -27251,17 +27226,17 @@
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>131260370</v>
+        <v>131260680</v>
       </c>
       <c r="B237" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27269,39 +27244,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>394001</v>
+        <v>393848</v>
       </c>
       <c r="R237" t="n">
-        <v>6950899</v>
+        <v>6950708</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27334,11 +27304,6 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>2 bild, tall, rikligt</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -27365,10 +27330,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>131258822</v>
+        <v>131258127</v>
       </c>
       <c r="B238" t="n">
-        <v>57884</v>
+        <v>91833</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -27376,39 +27341,30 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr"/>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>393926</v>
+        <v>393574</v>
       </c>
       <c r="R238" t="n">
-        <v>6951116</v>
+        <v>6950991</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27443,11 +27399,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>1 bild, gran</t>
-        </is>
-      </c>
       <c r="AD238" t="b">
         <v>0</v>
       </c>
@@ -27460,22 +27411,22 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>131259721</v>
+        <v>131258210</v>
       </c>
       <c r="B239" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27483,30 +27434,39 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>394066</v>
+        <v>393572</v>
       </c>
       <c r="R239" t="n">
-        <v>6951169</v>
+        <v>6951064</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27565,10 +27525,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>131258260</v>
+        <v>131260113</v>
       </c>
       <c r="B240" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27576,39 +27536,34 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>393671</v>
+        <v>394112</v>
       </c>
       <c r="R240" t="n">
-        <v>6951134</v>
+        <v>6951132</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27643,11 +27598,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC240" t="inlineStr">
-        <is>
-          <t>1 bild på tretåig hackspett</t>
-        </is>
-      </c>
       <c r="AD240" t="b">
         <v>0</v>
       </c>
@@ -27660,19 +27610,19 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>131260181</v>
+        <v>131259944</v>
       </c>
       <c r="B241" t="n">
         <v>57884</v>
@@ -27712,10 +27662,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>394066</v>
+        <v>394171</v>
       </c>
       <c r="R241" t="n">
-        <v>6951169</v>
+        <v>6951274</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27774,10 +27724,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>131258022</v>
+        <v>131259465</v>
       </c>
       <c r="B242" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27785,39 +27735,34 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>393593</v>
+        <v>393972</v>
       </c>
       <c r="R242" t="n">
-        <v>6951100</v>
+        <v>6951237</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27852,11 +27797,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>2 bild, gran</t>
-        </is>
-      </c>
       <c r="AD242" t="b">
         <v>0</v>
       </c>
@@ -27869,19 +27809,19 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>131259617</v>
+        <v>131259470</v>
       </c>
       <c r="B243" t="n">
         <v>57884</v>
@@ -27917,14 +27857,14 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>393858</v>
+        <v>393972</v>
       </c>
       <c r="R243" t="n">
-        <v>6951054</v>
+        <v>6951237</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27959,11 +27899,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>2 bild, gran</t>
-        </is>
-      </c>
       <c r="AD243" t="b">
         <v>0</v>
       </c>
@@ -27976,19 +27911,19 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>131257765</v>
+        <v>131260119</v>
       </c>
       <c r="B244" t="n">
         <v>57884</v>
@@ -28019,7 +27954,7 @@
       <c r="I244" t="inlineStr"/>
       <c r="M244" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
@@ -28028,10 +27963,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>393501</v>
+        <v>393903</v>
       </c>
       <c r="R244" t="n">
-        <v>6951126</v>
+        <v>6950826</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28068,7 +28003,7 @@
       </c>
       <c r="AC244" t="inlineStr">
         <is>
-          <t>1 bild, björk!</t>
+          <t>2 bild, gran</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -28095,7 +28030,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>131260677</v>
+        <v>131258863</v>
       </c>
       <c r="B245" t="n">
         <v>57884</v>
@@ -28126,7 +28061,7 @@
       <c r="I245" t="inlineStr"/>
       <c r="M245" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
@@ -28135,10 +28070,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>393848</v>
+        <v>393928</v>
       </c>
       <c r="R245" t="n">
-        <v>6950708</v>
+        <v>6951139</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -28175,7 +28110,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>1 bild, vid spår spillkråka</t>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -28195,17 +28130,17 @@
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>131257698</v>
+        <v>131257896</v>
       </c>
       <c r="B246" t="n">
-        <v>79245</v>
+        <v>91833</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28213,23 +28148,19 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
@@ -28237,10 +28168,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>393501</v>
+        <v>393554</v>
       </c>
       <c r="R246" t="n">
-        <v>6951126</v>
+        <v>6951144</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28299,45 +28230,50 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>131259937</v>
+        <v>131260485</v>
       </c>
       <c r="B247" t="n">
-        <v>83210</v>
+        <v>57881</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>306</v>
+        <v>100049</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>394158</v>
+        <v>393966</v>
       </c>
       <c r="R247" t="n">
-        <v>6951255</v>
+        <v>6950847</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28372,6 +28308,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>2 bild, högstubbe</t>
+        </is>
+      </c>
       <c r="AD247" t="b">
         <v>0</v>
       </c>
@@ -28384,22 +28325,22 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>131260680</v>
+        <v>131260664</v>
       </c>
       <c r="B248" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28407,24 +28348,29 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
@@ -28467,6 +28413,11 @@
       <c r="AA248" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>1 bild, tydliga hackhål</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28493,10 +28444,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>131258127</v>
+        <v>131260370</v>
       </c>
       <c r="B249" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28504,30 +28455,39 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>393574</v>
+        <v>394001</v>
       </c>
       <c r="R249" t="n">
-        <v>6950991</v>
+        <v>6950899</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28562,6 +28522,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>2 bild, tall, rikligt</t>
+        </is>
+      </c>
       <c r="AD249" t="b">
         <v>0</v>
       </c>
@@ -28574,19 +28539,19 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>131259825</v>
+        <v>131258822</v>
       </c>
       <c r="B250" t="n">
         <v>57884</v>
@@ -28617,7 +28582,7 @@
       <c r="I250" t="inlineStr"/>
       <c r="M250" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
@@ -28626,10 +28591,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>393904</v>
+        <v>393926</v>
       </c>
       <c r="R250" t="n">
-        <v>6950987</v>
+        <v>6951116</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28666,7 +28631,7 @@
       </c>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>2 bild, tall</t>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28693,27 +28658,27 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>131257444</v>
+        <v>131258260</v>
       </c>
       <c r="B251" t="n">
-        <v>57988</v>
+        <v>57884</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -28722,21 +28687,28 @@
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M251" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
+      <c r="N251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>393426</v>
+        <v>393671</v>
       </c>
       <c r="R251" t="n">
-        <v>6951191</v>
+        <v>6951134</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28769,6 +28741,11 @@
       <c r="AA251" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>1 bild på tretåig hackspett</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -28795,7 +28772,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>131257828</v>
+        <v>131258022</v>
       </c>
       <c r="B252" t="n">
         <v>57884</v>
@@ -28835,10 +28812,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>393999</v>
+        <v>393593</v>
       </c>
       <c r="R252" t="n">
-        <v>6951501</v>
+        <v>6951100</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28875,7 +28852,7 @@
       </c>
       <c r="AC252" t="inlineStr">
         <is>
-          <t>2 bild, gran lavskr</t>
+          <t>2 bild, gran</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28902,7 +28879,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>131258210</v>
+        <v>131259617</v>
       </c>
       <c r="B253" t="n">
         <v>57884</v>
@@ -28933,19 +28910,19 @@
       <c r="I253" t="inlineStr"/>
       <c r="M253" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>393572</v>
+        <v>393858</v>
       </c>
       <c r="R253" t="n">
-        <v>6951064</v>
+        <v>6951054</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28980,6 +28957,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>2 bild, gran</t>
+        </is>
+      </c>
       <c r="AD253" t="b">
         <v>0</v>
       </c>
@@ -28992,19 +28974,19 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>131260600</v>
+        <v>131260677</v>
       </c>
       <c r="B254" t="n">
         <v>57884</v>
@@ -29035,7 +29017,7 @@
       <c r="I254" t="inlineStr"/>
       <c r="M254" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
@@ -29044,10 +29026,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>393875</v>
+        <v>393848</v>
       </c>
       <c r="R254" t="n">
-        <v>6950773</v>
+        <v>6950708</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -29084,7 +29066,7 @@
       </c>
       <c r="AC254" t="inlineStr">
         <is>
-          <t>2 bild, tall</t>
+          <t>1 bild, vid spår spillkråka</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -29111,7 +29093,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>131259944</v>
+        <v>131259825</v>
       </c>
       <c r="B255" t="n">
         <v>57884</v>
@@ -29147,14 +29129,14 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>394171</v>
+        <v>393904</v>
       </c>
       <c r="R255" t="n">
-        <v>6951274</v>
+        <v>6950987</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29189,6 +29171,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
+        </is>
+      </c>
       <c r="AD255" t="b">
         <v>0</v>
       </c>
@@ -29201,57 +29188,62 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>131260113</v>
+        <v>131257444</v>
       </c>
       <c r="B256" t="n">
-        <v>79245</v>
+        <v>57988</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>394112</v>
+        <v>393426</v>
       </c>
       <c r="R256" t="n">
-        <v>6951132</v>
+        <v>6951191</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -29298,22 +29290,22 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>131259465</v>
+        <v>131257828</v>
       </c>
       <c r="B257" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -29321,34 +29313,39 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>393972</v>
+        <v>393999</v>
       </c>
       <c r="R257" t="n">
-        <v>6951237</v>
+        <v>6951501</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29383,6 +29380,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>2 bild, gran lavskr</t>
+        </is>
+      </c>
       <c r="AD257" t="b">
         <v>0</v>
       </c>
@@ -29395,19 +29397,19 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>131259470</v>
+        <v>131260600</v>
       </c>
       <c r="B258" t="n">
         <v>57884</v>
@@ -29443,14 +29445,14 @@
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>393972</v>
+        <v>393875</v>
       </c>
       <c r="R258" t="n">
-        <v>6951237</v>
+        <v>6950773</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29485,6 +29487,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
+        </is>
+      </c>
       <c r="AD258" t="b">
         <v>0</v>
       </c>
@@ -29497,12 +29504,12 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -25452,7 +25452,7 @@
         <v>131260454</v>
       </c>
       <c r="B219" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>131259806</v>
+        <v>131258518</v>
       </c>
       <c r="B220" t="n">
         <v>57884</v>
@@ -25577,19 +25577,19 @@
       <c r="I220" t="inlineStr"/>
       <c r="M220" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>394106</v>
+        <v>393763</v>
       </c>
       <c r="R220" t="n">
-        <v>6951186</v>
+        <v>6951214</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25648,7 +25648,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>131258518</v>
+        <v>131259806</v>
       </c>
       <c r="B221" t="n">
         <v>57884</v>
@@ -25679,19 +25679,19 @@
       <c r="I221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>393763</v>
+        <v>394106</v>
       </c>
       <c r="R221" t="n">
-        <v>6951214</v>
+        <v>6951186</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25750,10 +25750,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>131257750</v>
+        <v>131259983</v>
       </c>
       <c r="B222" t="n">
-        <v>83225</v>
+        <v>57884</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25761,34 +25761,39 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>393518</v>
+        <v>394187</v>
       </c>
       <c r="R222" t="n">
-        <v>6951114</v>
+        <v>6951218</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25847,10 +25852,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>131259983</v>
+        <v>131257750</v>
       </c>
       <c r="B223" t="n">
-        <v>57884</v>
+        <v>83226</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25858,39 +25863,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>394187</v>
+        <v>393518</v>
       </c>
       <c r="R223" t="n">
-        <v>6951218</v>
+        <v>6951114</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25952,7 +25952,7 @@
         <v>131257777</v>
       </c>
       <c r="B224" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>131259760</v>
       </c>
       <c r="B225" t="n">
-        <v>83225</v>
+        <v>83226</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26241,10 +26241,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>131259701</v>
+        <v>131257647</v>
       </c>
       <c r="B227" t="n">
-        <v>57884</v>
+        <v>83226</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26252,39 +26252,34 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>394058</v>
+        <v>393444</v>
       </c>
       <c r="R227" t="n">
-        <v>6951183</v>
+        <v>6951119</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26343,10 +26338,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>131259451</v>
+        <v>131259701</v>
       </c>
       <c r="B228" t="n">
-        <v>91833</v>
+        <v>57884</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26354,30 +26349,39 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>393972</v>
+        <v>394058</v>
       </c>
       <c r="R228" t="n">
-        <v>6951237</v>
+        <v>6951183</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26436,10 +26440,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>131257647</v>
+        <v>131258105</v>
       </c>
       <c r="B229" t="n">
-        <v>83225</v>
+        <v>57884</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26447,34 +26451,39 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>393444</v>
+        <v>393564</v>
       </c>
       <c r="R229" t="n">
-        <v>6951119</v>
+        <v>6950996</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26533,10 +26542,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>131258105</v>
+        <v>131259451</v>
       </c>
       <c r="B230" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26544,39 +26553,30 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>393564</v>
+        <v>393972</v>
       </c>
       <c r="R230" t="n">
-        <v>6950996</v>
+        <v>6951237</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26740,7 +26740,7 @@
         <v>131259721</v>
       </c>
       <c r="B232" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>131259937</v>
       </c>
       <c r="B235" t="n">
-        <v>83210</v>
+        <v>83211</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27136,10 +27136,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>131257698</v>
+        <v>131258127</v>
       </c>
       <c r="B236" t="n">
-        <v>79245</v>
+        <v>91834</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27147,34 +27147,30 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>393501</v>
+        <v>393574</v>
       </c>
       <c r="R236" t="n">
-        <v>6951126</v>
+        <v>6950991</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27221,22 +27217,22 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>131260680</v>
+        <v>131257698</v>
       </c>
       <c r="B237" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27268,10 +27264,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>393848</v>
+        <v>393501</v>
       </c>
       <c r="R237" t="n">
-        <v>6950708</v>
+        <v>6951126</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27323,17 +27319,17 @@
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>131258127</v>
+        <v>131260680</v>
       </c>
       <c r="B238" t="n">
-        <v>91833</v>
+        <v>79246</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -27341,30 +27337,34 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>393574</v>
+        <v>393848</v>
       </c>
       <c r="R238" t="n">
-        <v>6950991</v>
+        <v>6950708</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27411,12 +27411,12 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
@@ -27528,7 +27528,7 @@
         <v>131260113</v>
       </c>
       <c r="B240" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>131259465</v>
       </c>
       <c r="B242" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28137,10 +28137,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>131257896</v>
+        <v>131260664</v>
       </c>
       <c r="B246" t="n">
-        <v>91833</v>
+        <v>57881</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28148,30 +28148,39 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>393554</v>
+        <v>393848</v>
       </c>
       <c r="R246" t="n">
-        <v>6951144</v>
+        <v>6950708</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28206,6 +28215,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>1 bild, tydliga hackhål</t>
+        </is>
+      </c>
       <c r="AD246" t="b">
         <v>0</v>
       </c>
@@ -28223,7 +28237,7 @@
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
@@ -28337,10 +28351,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>131260664</v>
+        <v>131258822</v>
       </c>
       <c r="B248" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28348,16 +28362,16 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -28368,7 +28382,7 @@
       <c r="I248" t="inlineStr"/>
       <c r="M248" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
@@ -28377,10 +28391,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>393848</v>
+        <v>393926</v>
       </c>
       <c r="R248" t="n">
-        <v>6950708</v>
+        <v>6951116</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28417,7 +28431,7 @@
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>1 bild, tydliga hackhål</t>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28437,17 +28451,17 @@
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>131260370</v>
+        <v>131257896</v>
       </c>
       <c r="B249" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28455,39 +28469,30 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P249" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>394001</v>
+        <v>393554</v>
       </c>
       <c r="R249" t="n">
-        <v>6950899</v>
+        <v>6951144</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28522,11 +28527,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>2 bild, tall, rikligt</t>
-        </is>
-      </c>
       <c r="AD249" t="b">
         <v>0</v>
       </c>
@@ -28544,14 +28544,14 @@
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>131258822</v>
+        <v>131260370</v>
       </c>
       <c r="B250" t="n">
         <v>57884</v>
@@ -28582,7 +28582,7 @@
       <c r="I250" t="inlineStr"/>
       <c r="M250" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
@@ -28591,10 +28591,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>393926</v>
+        <v>394001</v>
       </c>
       <c r="R250" t="n">
-        <v>6951116</v>
+        <v>6950899</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28631,7 +28631,7 @@
       </c>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>1 bild, gran</t>
+          <t>2 bild, tall, rikligt</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28651,7 +28651,7 @@
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -26241,10 +26241,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>131257647</v>
+        <v>131259451</v>
       </c>
       <c r="B227" t="n">
-        <v>83226</v>
+        <v>91834</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26252,23 +26252,19 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
@@ -26276,10 +26272,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>393444</v>
+        <v>393972</v>
       </c>
       <c r="R227" t="n">
-        <v>6951119</v>
+        <v>6951237</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26338,10 +26334,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>131259701</v>
+        <v>131257647</v>
       </c>
       <c r="B228" t="n">
-        <v>57884</v>
+        <v>83226</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26349,39 +26345,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>394058</v>
+        <v>393444</v>
       </c>
       <c r="R228" t="n">
-        <v>6951183</v>
+        <v>6951119</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26440,7 +26431,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>131258105</v>
+        <v>131259701</v>
       </c>
       <c r="B229" t="n">
         <v>57884</v>
@@ -26476,14 +26467,14 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>393564</v>
+        <v>394058</v>
       </c>
       <c r="R229" t="n">
-        <v>6950996</v>
+        <v>6951183</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26542,10 +26533,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>131259451</v>
+        <v>131258105</v>
       </c>
       <c r="B230" t="n">
-        <v>91834</v>
+        <v>57884</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26553,30 +26544,39 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>393972</v>
+        <v>393564</v>
       </c>
       <c r="R230" t="n">
-        <v>6951237</v>
+        <v>6950996</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -27525,10 +27525,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>131260113</v>
+        <v>131259944</v>
       </c>
       <c r="B240" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27536,34 +27536,39 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>394112</v>
+        <v>394171</v>
       </c>
       <c r="R240" t="n">
-        <v>6951132</v>
+        <v>6951274</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27622,10 +27627,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>131259944</v>
+        <v>131260113</v>
       </c>
       <c r="B241" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27633,39 +27638,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P241" t="inlineStr">
         <is>
           <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>394171</v>
+        <v>394112</v>
       </c>
       <c r="R241" t="n">
-        <v>6951274</v>
+        <v>6951132</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -25452,7 +25452,7 @@
         <v>131260454</v>
       </c>
       <c r="B219" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>131258518</v>
       </c>
       <c r="B220" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>131259806</v>
       </c>
       <c r="B221" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25750,10 +25750,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>131259983</v>
+        <v>131257750</v>
       </c>
       <c r="B222" t="n">
-        <v>57884</v>
+        <v>83228</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25761,39 +25761,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>394187</v>
+        <v>393518</v>
       </c>
       <c r="R222" t="n">
-        <v>6951218</v>
+        <v>6951114</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25852,10 +25847,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>131257750</v>
+        <v>131259983</v>
       </c>
       <c r="B223" t="n">
-        <v>83226</v>
+        <v>57886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25863,34 +25858,39 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>393518</v>
+        <v>394187</v>
       </c>
       <c r="R223" t="n">
-        <v>6951114</v>
+        <v>6951218</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25952,7 +25952,7 @@
         <v>131257777</v>
       </c>
       <c r="B224" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>131259760</v>
       </c>
       <c r="B225" t="n">
-        <v>83226</v>
+        <v>83228</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>131260234</v>
       </c>
       <c r="B226" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>131259451</v>
       </c>
       <c r="B227" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>131257647</v>
       </c>
       <c r="B228" t="n">
-        <v>83226</v>
+        <v>83228</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>131259701</v>
       </c>
       <c r="B229" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>131258105</v>
       </c>
       <c r="B230" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>131258813</v>
       </c>
       <c r="B231" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>131259721</v>
       </c>
       <c r="B232" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>131260181</v>
       </c>
       <c r="B233" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>131257765</v>
       </c>
       <c r="B234" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>131259937</v>
       </c>
       <c r="B235" t="n">
-        <v>83211</v>
+        <v>83213</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27136,10 +27136,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>131258127</v>
+        <v>131257698</v>
       </c>
       <c r="B236" t="n">
-        <v>91834</v>
+        <v>79248</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27147,30 +27147,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>393574</v>
+        <v>393501</v>
       </c>
       <c r="R236" t="n">
-        <v>6950991</v>
+        <v>6951126</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27217,22 +27221,22 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>131257698</v>
+        <v>131260680</v>
       </c>
       <c r="B237" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27264,10 +27268,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>393501</v>
+        <v>393848</v>
       </c>
       <c r="R237" t="n">
-        <v>6951126</v>
+        <v>6950708</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27319,17 +27323,17 @@
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>131260680</v>
+        <v>131258127</v>
       </c>
       <c r="B238" t="n">
-        <v>79246</v>
+        <v>91836</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -27337,34 +27341,30 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>393848</v>
+        <v>393574</v>
       </c>
       <c r="R238" t="n">
-        <v>6950708</v>
+        <v>6950991</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27411,12 +27411,12 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
@@ -27426,7 +27426,7 @@
         <v>131258210</v>
       </c>
       <c r="B239" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27525,10 +27525,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>131259944</v>
+        <v>131260113</v>
       </c>
       <c r="B240" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27536,39 +27536,34 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>394171</v>
+        <v>394112</v>
       </c>
       <c r="R240" t="n">
-        <v>6951274</v>
+        <v>6951132</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27627,10 +27622,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>131260113</v>
+        <v>131259944</v>
       </c>
       <c r="B241" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27638,34 +27633,39 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P241" t="inlineStr">
         <is>
           <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>394112</v>
+        <v>394171</v>
       </c>
       <c r="R241" t="n">
-        <v>6951132</v>
+        <v>6951274</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27727,7 +27727,7 @@
         <v>131259465</v>
       </c>
       <c r="B242" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>131259470</v>
       </c>
       <c r="B243" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>131260119</v>
       </c>
       <c r="B244" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>131258863</v>
       </c>
       <c r="B245" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28137,10 +28137,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>131260664</v>
+        <v>131257896</v>
       </c>
       <c r="B246" t="n">
-        <v>57881</v>
+        <v>91836</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28148,39 +28148,30 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>393848</v>
+        <v>393554</v>
       </c>
       <c r="R246" t="n">
-        <v>6950708</v>
+        <v>6951144</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28215,11 +28206,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>1 bild, tydliga hackhål</t>
-        </is>
-      </c>
       <c r="AD246" t="b">
         <v>0</v>
       </c>
@@ -28237,17 +28223,17 @@
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>131260485</v>
+        <v>131260664</v>
       </c>
       <c r="B247" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28284,10 +28270,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>393966</v>
+        <v>393848</v>
       </c>
       <c r="R247" t="n">
-        <v>6950847</v>
+        <v>6950708</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28324,7 +28310,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>2 bild, högstubbe</t>
+          <t>1 bild, tydliga hackhål</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28351,10 +28337,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>131258822</v>
+        <v>131260485</v>
       </c>
       <c r="B248" t="n">
-        <v>57884</v>
+        <v>57883</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28362,16 +28348,16 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -28382,7 +28368,7 @@
       <c r="I248" t="inlineStr"/>
       <c r="M248" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
@@ -28391,10 +28377,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>393926</v>
+        <v>393966</v>
       </c>
       <c r="R248" t="n">
-        <v>6951116</v>
+        <v>6950847</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28431,7 +28417,7 @@
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>1 bild, gran</t>
+          <t>2 bild, högstubbe</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28451,17 +28437,17 @@
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>131257896</v>
+        <v>131260370</v>
       </c>
       <c r="B249" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28469,30 +28455,39 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P249" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>393554</v>
+        <v>394001</v>
       </c>
       <c r="R249" t="n">
-        <v>6951144</v>
+        <v>6950899</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28527,6 +28522,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>2 bild, tall, rikligt</t>
+        </is>
+      </c>
       <c r="AD249" t="b">
         <v>0</v>
       </c>
@@ -28544,17 +28544,17 @@
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>131260370</v>
+        <v>131258822</v>
       </c>
       <c r="B250" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
       <c r="I250" t="inlineStr"/>
       <c r="M250" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
@@ -28591,10 +28591,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>394001</v>
+        <v>393926</v>
       </c>
       <c r="R250" t="n">
-        <v>6950899</v>
+        <v>6951116</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28631,7 +28631,7 @@
       </c>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>2 bild, tall, rikligt</t>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28651,7 +28651,7 @@
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
@@ -28661,7 +28661,7 @@
         <v>131258260</v>
       </c>
       <c r="B251" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>131258022</v>
       </c>
       <c r="B252" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>131259617</v>
       </c>
       <c r="B253" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
         <v>131260677</v>
       </c>
       <c r="B254" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29093,27 +29093,27 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>131259825</v>
+        <v>131257444</v>
       </c>
       <c r="B255" t="n">
-        <v>57884</v>
+        <v>57990</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -29124,7 +29124,7 @@
       <c r="I255" t="inlineStr"/>
       <c r="M255" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
@@ -29133,10 +29133,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>393904</v>
+        <v>393426</v>
       </c>
       <c r="R255" t="n">
-        <v>6950987</v>
+        <v>6951191</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29169,11 +29169,6 @@
       <c r="AA255" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29200,27 +29195,27 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>131257444</v>
+        <v>131259825</v>
       </c>
       <c r="B256" t="n">
-        <v>57988</v>
+        <v>57886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -29231,7 +29226,7 @@
       <c r="I256" t="inlineStr"/>
       <c r="M256" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
@@ -29240,10 +29235,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>393426</v>
+        <v>393904</v>
       </c>
       <c r="R256" t="n">
-        <v>6951191</v>
+        <v>6950987</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -29276,6 +29271,11 @@
       <c r="AA256" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -29305,7 +29305,7 @@
         <v>131257828</v>
       </c>
       <c r="B257" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>131260600</v>
       </c>
       <c r="B258" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -25452,7 +25452,7 @@
         <v>131260454</v>
       </c>
       <c r="B219" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25546,10 +25546,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>131258518</v>
+        <v>131259806</v>
       </c>
       <c r="B220" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25577,19 +25577,19 @@
       <c r="I220" t="inlineStr"/>
       <c r="M220" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>393763</v>
+        <v>394106</v>
       </c>
       <c r="R220" t="n">
-        <v>6951214</v>
+        <v>6951186</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25648,10 +25648,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>131259806</v>
+        <v>131258518</v>
       </c>
       <c r="B221" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25679,19 +25679,19 @@
       <c r="I221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>394106</v>
+        <v>393763</v>
       </c>
       <c r="R221" t="n">
-        <v>6951186</v>
+        <v>6951214</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25753,7 +25753,7 @@
         <v>131257750</v>
       </c>
       <c r="B222" t="n">
-        <v>83228</v>
+        <v>83229</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>131259983</v>
       </c>
       <c r="B223" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>131257777</v>
       </c>
       <c r="B224" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>131259760</v>
       </c>
       <c r="B225" t="n">
-        <v>83228</v>
+        <v>83229</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>131260234</v>
       </c>
       <c r="B226" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26241,10 +26241,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>131259451</v>
+        <v>131257647</v>
       </c>
       <c r="B227" t="n">
-        <v>91836</v>
+        <v>83229</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26252,19 +26252,23 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
@@ -26272,10 +26276,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>393972</v>
+        <v>393444</v>
       </c>
       <c r="R227" t="n">
-        <v>6951237</v>
+        <v>6951119</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26334,10 +26338,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>131257647</v>
+        <v>131259701</v>
       </c>
       <c r="B228" t="n">
-        <v>83228</v>
+        <v>57887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26345,34 +26349,39 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>393444</v>
+        <v>394058</v>
       </c>
       <c r="R228" t="n">
-        <v>6951119</v>
+        <v>6951183</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26431,10 +26440,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>131259701</v>
+        <v>131258105</v>
       </c>
       <c r="B229" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26467,14 +26476,14 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>394058</v>
+        <v>393564</v>
       </c>
       <c r="R229" t="n">
-        <v>6951183</v>
+        <v>6950996</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26533,10 +26542,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>131258105</v>
+        <v>131259451</v>
       </c>
       <c r="B230" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26544,39 +26553,30 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>393564</v>
+        <v>393972</v>
       </c>
       <c r="R230" t="n">
-        <v>6950996</v>
+        <v>6951237</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26638,7 +26638,7 @@
         <v>131258813</v>
       </c>
       <c r="B231" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>131259721</v>
       </c>
       <c r="B232" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>131260181</v>
       </c>
       <c r="B233" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>131257765</v>
       </c>
       <c r="B234" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27039,45 +27039,45 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>131259937</v>
+        <v>131257698</v>
       </c>
       <c r="B235" t="n">
-        <v>83213</v>
+        <v>79249</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>394158</v>
+        <v>393501</v>
       </c>
       <c r="R235" t="n">
-        <v>6951255</v>
+        <v>6951126</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27124,22 +27124,22 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>131257698</v>
+        <v>131260680</v>
       </c>
       <c r="B236" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27171,10 +27171,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>393501</v>
+        <v>393848</v>
       </c>
       <c r="R236" t="n">
-        <v>6951126</v>
+        <v>6950708</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27226,52 +27226,52 @@
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>131260680</v>
+        <v>131259937</v>
       </c>
       <c r="B237" t="n">
-        <v>79248</v>
+        <v>83214</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>393848</v>
+        <v>394158</v>
       </c>
       <c r="R237" t="n">
-        <v>6950708</v>
+        <v>6951255</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27318,12 +27318,12 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
@@ -27333,7 +27333,7 @@
         <v>131258127</v>
       </c>
       <c r="B238" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>131258210</v>
       </c>
       <c r="B239" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>131260113</v>
       </c>
       <c r="B240" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>131259944</v>
       </c>
       <c r="B241" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>131259465</v>
       </c>
       <c r="B242" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>131259470</v>
       </c>
       <c r="B243" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>131260119</v>
       </c>
       <c r="B244" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>131258863</v>
       </c>
       <c r="B245" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28137,10 +28137,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>131257896</v>
+        <v>131260370</v>
       </c>
       <c r="B246" t="n">
-        <v>91836</v>
+        <v>57887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28148,30 +28148,39 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>393554</v>
+        <v>394001</v>
       </c>
       <c r="R246" t="n">
-        <v>6951144</v>
+        <v>6950899</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28206,6 +28215,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>2 bild, tall, rikligt</t>
+        </is>
+      </c>
       <c r="AD246" t="b">
         <v>0</v>
       </c>
@@ -28223,17 +28237,17 @@
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>131260664</v>
+        <v>131258822</v>
       </c>
       <c r="B247" t="n">
-        <v>57883</v>
+        <v>57887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28241,16 +28255,16 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -28261,7 +28275,7 @@
       <c r="I247" t="inlineStr"/>
       <c r="M247" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
@@ -28270,10 +28284,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>393848</v>
+        <v>393926</v>
       </c>
       <c r="R247" t="n">
-        <v>6950708</v>
+        <v>6951116</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28310,7 +28324,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>1 bild, tydliga hackhål</t>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28330,17 +28344,17 @@
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>131260485</v>
+        <v>131260664</v>
       </c>
       <c r="B248" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28377,10 +28391,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>393966</v>
+        <v>393848</v>
       </c>
       <c r="R248" t="n">
-        <v>6950847</v>
+        <v>6950708</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28417,7 +28431,7 @@
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>2 bild, högstubbe</t>
+          <t>1 bild, tydliga hackhål</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28444,10 +28458,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>131260370</v>
+        <v>131260485</v>
       </c>
       <c r="B249" t="n">
-        <v>57886</v>
+        <v>57884</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28455,16 +28469,16 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -28484,10 +28498,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>394001</v>
+        <v>393966</v>
       </c>
       <c r="R249" t="n">
-        <v>6950899</v>
+        <v>6950847</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28524,7 +28538,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>2 bild, tall, rikligt</t>
+          <t>2 bild, högstubbe</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28551,10 +28565,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>131258822</v>
+        <v>131257896</v>
       </c>
       <c r="B250" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28562,39 +28576,30 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr"/>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P250" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>393926</v>
+        <v>393554</v>
       </c>
       <c r="R250" t="n">
-        <v>6951116</v>
+        <v>6951144</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28627,11 +28632,6 @@
       <c r="AA250" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28661,7 +28661,7 @@
         <v>131258260</v>
       </c>
       <c r="B251" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
@@ -28775,7 +28775,7 @@
         <v>131258022</v>
       </c>
       <c r="B252" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>131259617</v>
       </c>
       <c r="B253" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
         <v>131260677</v>
       </c>
       <c r="B254" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29093,27 +29093,27 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>131257444</v>
+        <v>131259825</v>
       </c>
       <c r="B255" t="n">
-        <v>57990</v>
+        <v>57887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -29124,7 +29124,7 @@
       <c r="I255" t="inlineStr"/>
       <c r="M255" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
@@ -29133,10 +29133,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>393426</v>
+        <v>393904</v>
       </c>
       <c r="R255" t="n">
-        <v>6951191</v>
+        <v>6950987</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29169,6 +29169,11 @@
       <c r="AA255" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29195,27 +29200,27 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>131259825</v>
+        <v>131257444</v>
       </c>
       <c r="B256" t="n">
-        <v>57886</v>
+        <v>57991</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -29226,7 +29231,7 @@
       <c r="I256" t="inlineStr"/>
       <c r="M256" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
@@ -29235,10 +29240,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>393904</v>
+        <v>393426</v>
       </c>
       <c r="R256" t="n">
-        <v>6950987</v>
+        <v>6951191</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -29271,11 +29276,6 @@
       <c r="AA256" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -29305,7 +29305,7 @@
         <v>131257828</v>
       </c>
       <c r="B257" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>131260600</v>
       </c>
       <c r="B258" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -25546,7 +25546,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>131259806</v>
+        <v>131258518</v>
       </c>
       <c r="B220" t="n">
         <v>57887</v>
@@ -25577,19 +25577,19 @@
       <c r="I220" t="inlineStr"/>
       <c r="M220" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>394106</v>
+        <v>393763</v>
       </c>
       <c r="R220" t="n">
-        <v>6951186</v>
+        <v>6951214</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25648,7 +25648,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>131258518</v>
+        <v>131259806</v>
       </c>
       <c r="B221" t="n">
         <v>57887</v>
@@ -25679,19 +25679,19 @@
       <c r="I221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>393763</v>
+        <v>394106</v>
       </c>
       <c r="R221" t="n">
-        <v>6951214</v>
+        <v>6951186</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -26241,10 +26241,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>131257647</v>
+        <v>131259701</v>
       </c>
       <c r="B227" t="n">
-        <v>83229</v>
+        <v>57887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26252,34 +26252,39 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>393444</v>
+        <v>394058</v>
       </c>
       <c r="R227" t="n">
-        <v>6951119</v>
+        <v>6951183</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26338,10 +26343,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>131259701</v>
+        <v>131259451</v>
       </c>
       <c r="B228" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26349,39 +26354,30 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>394058</v>
+        <v>393972</v>
       </c>
       <c r="R228" t="n">
-        <v>6951183</v>
+        <v>6951237</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26440,10 +26436,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>131258105</v>
+        <v>131257647</v>
       </c>
       <c r="B229" t="n">
-        <v>57887</v>
+        <v>83229</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26451,39 +26447,34 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>393564</v>
+        <v>393444</v>
       </c>
       <c r="R229" t="n">
-        <v>6950996</v>
+        <v>6951119</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26542,10 +26533,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>131259451</v>
+        <v>131258105</v>
       </c>
       <c r="B230" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26553,30 +26544,39 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>393972</v>
+        <v>393564</v>
       </c>
       <c r="R230" t="n">
-        <v>6951237</v>
+        <v>6950996</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -27233,45 +27233,41 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>131259937</v>
+        <v>131258127</v>
       </c>
       <c r="B237" t="n">
-        <v>83214</v>
+        <v>91837</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>306</v>
+        <v>5432</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>394158</v>
+        <v>393574</v>
       </c>
       <c r="R237" t="n">
-        <v>6951255</v>
+        <v>6950991</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27330,41 +27326,45 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>131258127</v>
+        <v>131259937</v>
       </c>
       <c r="B238" t="n">
-        <v>91837</v>
+        <v>83214</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>5432</v>
+        <v>306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr"/>
+          <t>Chaenotheca chlorella</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>393574</v>
+        <v>394158</v>
       </c>
       <c r="R238" t="n">
-        <v>6950991</v>
+        <v>6951255</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27724,10 +27724,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>131259465</v>
+        <v>131259470</v>
       </c>
       <c r="B242" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27735,24 +27735,29 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P242" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
@@ -27821,10 +27826,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>131259470</v>
+        <v>131259465</v>
       </c>
       <c r="B243" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27832,29 +27837,24 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
@@ -28765,7 +28765,7 @@
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -26241,10 +26241,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>131259701</v>
+        <v>131259451</v>
       </c>
       <c r="B227" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26252,39 +26252,30 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>394058</v>
+        <v>393972</v>
       </c>
       <c r="R227" t="n">
-        <v>6951183</v>
+        <v>6951237</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26343,10 +26334,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>131259451</v>
+        <v>131257647</v>
       </c>
       <c r="B228" t="n">
-        <v>91837</v>
+        <v>83229</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26354,19 +26345,23 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
@@ -26374,10 +26369,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>393972</v>
+        <v>393444</v>
       </c>
       <c r="R228" t="n">
-        <v>6951237</v>
+        <v>6951119</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26436,10 +26431,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>131257647</v>
+        <v>131259701</v>
       </c>
       <c r="B229" t="n">
-        <v>83229</v>
+        <v>57887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26447,34 +26442,39 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>393444</v>
+        <v>394058</v>
       </c>
       <c r="R229" t="n">
-        <v>6951119</v>
+        <v>6951183</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -27039,10 +27039,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>131257698</v>
+        <v>131258127</v>
       </c>
       <c r="B235" t="n">
-        <v>79249</v>
+        <v>91837</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27050,34 +27050,30 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>393501</v>
+        <v>393574</v>
       </c>
       <c r="R235" t="n">
-        <v>6951126</v>
+        <v>6950991</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27124,19 +27120,19 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>131260680</v>
+        <v>131257698</v>
       </c>
       <c r="B236" t="n">
         <v>79249</v>
@@ -27171,10 +27167,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>393848</v>
+        <v>393501</v>
       </c>
       <c r="R236" t="n">
-        <v>6950708</v>
+        <v>6951126</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27226,17 +27222,17 @@
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>131258127</v>
+        <v>131260680</v>
       </c>
       <c r="B237" t="n">
-        <v>91837</v>
+        <v>79249</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27244,30 +27240,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>393574</v>
+        <v>393848</v>
       </c>
       <c r="R237" t="n">
-        <v>6950991</v>
+        <v>6950708</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27314,12 +27314,12 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
@@ -27525,10 +27525,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>131260113</v>
+        <v>131259944</v>
       </c>
       <c r="B240" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27536,34 +27536,39 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>394112</v>
+        <v>394171</v>
       </c>
       <c r="R240" t="n">
-        <v>6951132</v>
+        <v>6951274</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27622,10 +27627,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>131259944</v>
+        <v>131260113</v>
       </c>
       <c r="B241" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27633,39 +27638,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P241" t="inlineStr">
         <is>
           <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>394171</v>
+        <v>394112</v>
       </c>
       <c r="R241" t="n">
-        <v>6951274</v>
+        <v>6951132</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27724,10 +27724,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>131259470</v>
+        <v>131259465</v>
       </c>
       <c r="B242" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27735,29 +27735,24 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P242" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
@@ -27826,10 +27821,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>131259465</v>
+        <v>131259470</v>
       </c>
       <c r="B243" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27837,24 +27832,29 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
@@ -28137,10 +28137,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>131260370</v>
+        <v>131257896</v>
       </c>
       <c r="B246" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28148,39 +28148,30 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>394001</v>
+        <v>393554</v>
       </c>
       <c r="R246" t="n">
-        <v>6950899</v>
+        <v>6951144</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28215,11 +28206,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>2 bild, tall, rikligt</t>
-        </is>
-      </c>
       <c r="AD246" t="b">
         <v>0</v>
       </c>
@@ -28237,7 +28223,7 @@
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
@@ -28351,10 +28337,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>131260664</v>
+        <v>131260370</v>
       </c>
       <c r="B248" t="n">
-        <v>57884</v>
+        <v>57887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28362,16 +28348,16 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -28391,10 +28377,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>393848</v>
+        <v>394001</v>
       </c>
       <c r="R248" t="n">
-        <v>6950708</v>
+        <v>6950899</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28431,7 +28417,7 @@
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>1 bild, tydliga hackhål</t>
+          <t>2 bild, tall, rikligt</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28458,7 +28444,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>131260485</v>
+        <v>131260664</v>
       </c>
       <c r="B249" t="n">
         <v>57884</v>
@@ -28498,10 +28484,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>393966</v>
+        <v>393848</v>
       </c>
       <c r="R249" t="n">
-        <v>6950847</v>
+        <v>6950708</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28538,7 +28524,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>2 bild, högstubbe</t>
+          <t>1 bild, tydliga hackhål</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28565,10 +28551,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>131257896</v>
+        <v>131260485</v>
       </c>
       <c r="B250" t="n">
-        <v>91837</v>
+        <v>57884</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28576,30 +28562,39 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P250" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>393554</v>
+        <v>393966</v>
       </c>
       <c r="R250" t="n">
-        <v>6951144</v>
+        <v>6950847</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28634,6 +28629,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>2 bild, högstubbe</t>
+        </is>
+      </c>
       <c r="AD250" t="b">
         <v>0</v>
       </c>
@@ -28651,7 +28651,7 @@
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
@@ -28772,7 +28772,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>131258022</v>
+        <v>131259617</v>
       </c>
       <c r="B252" t="n">
         <v>57887</v>
@@ -28812,10 +28812,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>393593</v>
+        <v>393858</v>
       </c>
       <c r="R252" t="n">
-        <v>6951100</v>
+        <v>6951054</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28879,7 +28879,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>131259617</v>
+        <v>131258022</v>
       </c>
       <c r="B253" t="n">
         <v>57887</v>
@@ -28919,10 +28919,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>393858</v>
+        <v>393593</v>
       </c>
       <c r="R253" t="n">
-        <v>6951054</v>
+        <v>6951100</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -25452,7 +25452,7 @@
         <v>131260454</v>
       </c>
       <c r="B219" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>131258518</v>
       </c>
       <c r="B220" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>131259806</v>
       </c>
       <c r="B221" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25750,10 +25750,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>131259983</v>
+        <v>131257750</v>
       </c>
       <c r="B222" t="n">
-        <v>57892</v>
+        <v>83240</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25761,39 +25761,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>394187</v>
+        <v>393518</v>
       </c>
       <c r="R222" t="n">
-        <v>6951218</v>
+        <v>6951114</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25852,10 +25847,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>131257750</v>
+        <v>131259983</v>
       </c>
       <c r="B223" t="n">
-        <v>83234</v>
+        <v>57898</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25863,34 +25858,39 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>393518</v>
+        <v>394187</v>
       </c>
       <c r="R223" t="n">
-        <v>6951114</v>
+        <v>6951218</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25952,7 +25952,7 @@
         <v>131257777</v>
       </c>
       <c r="B224" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26042,10 +26042,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>131259760</v>
+        <v>131260234</v>
       </c>
       <c r="B225" t="n">
-        <v>83234</v>
+        <v>57898</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26053,34 +26053,39 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>394099</v>
+        <v>394049</v>
       </c>
       <c r="R225" t="n">
-        <v>6951193</v>
+        <v>6951150</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26139,10 +26144,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>131260234</v>
+        <v>131259760</v>
       </c>
       <c r="B226" t="n">
-        <v>57892</v>
+        <v>83240</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26150,39 +26155,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>394049</v>
+        <v>394099</v>
       </c>
       <c r="R226" t="n">
-        <v>6951150</v>
+        <v>6951193</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26244,7 +26244,7 @@
         <v>131259451</v>
       </c>
       <c r="B227" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>131257647</v>
       </c>
       <c r="B228" t="n">
-        <v>83234</v>
+        <v>83240</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>131259701</v>
       </c>
       <c r="B229" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>131258105</v>
       </c>
       <c r="B230" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>131258813</v>
       </c>
       <c r="B231" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>131259721</v>
       </c>
       <c r="B232" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26830,10 +26830,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>131257765</v>
+        <v>131260181</v>
       </c>
       <c r="B233" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26861,19 +26861,19 @@
       <c r="I233" t="inlineStr"/>
       <c r="M233" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>393501</v>
+        <v>394066</v>
       </c>
       <c r="R233" t="n">
-        <v>6951126</v>
+        <v>6951169</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26908,11 +26908,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>1 bild, björk!</t>
-        </is>
-      </c>
       <c r="AD233" t="b">
         <v>0</v>
       </c>
@@ -26925,22 +26920,22 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>131260181</v>
+        <v>131257765</v>
       </c>
       <c r="B234" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26968,19 +26963,19 @@
       <c r="I234" t="inlineStr"/>
       <c r="M234" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>394066</v>
+        <v>393501</v>
       </c>
       <c r="R234" t="n">
-        <v>6951169</v>
+        <v>6951126</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27015,6 +27010,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>1 bild, björk!</t>
+        </is>
+      </c>
       <c r="AD234" t="b">
         <v>0</v>
       </c>
@@ -27027,12 +27027,12 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
@@ -27042,7 +27042,7 @@
         <v>131259937</v>
       </c>
       <c r="B235" t="n">
-        <v>83219</v>
+        <v>83225</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27136,10 +27136,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>131260680</v>
+        <v>131258127</v>
       </c>
       <c r="B236" t="n">
-        <v>79254</v>
+        <v>91848</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27147,34 +27147,30 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>393848</v>
+        <v>393574</v>
       </c>
       <c r="R236" t="n">
-        <v>6950708</v>
+        <v>6950991</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27221,22 +27217,22 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>131258127</v>
+        <v>131257698</v>
       </c>
       <c r="B237" t="n">
-        <v>91842</v>
+        <v>79260</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27244,30 +27240,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>393574</v>
+        <v>393501</v>
       </c>
       <c r="R237" t="n">
-        <v>6950991</v>
+        <v>6951126</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27314,22 +27314,22 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>131257698</v>
+        <v>131260680</v>
       </c>
       <c r="B238" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -27361,10 +27361,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>393501</v>
+        <v>393848</v>
       </c>
       <c r="R238" t="n">
-        <v>6951126</v>
+        <v>6950708</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27416,7 +27416,7 @@
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
@@ -27426,7 +27426,7 @@
         <v>131258210</v>
       </c>
       <c r="B239" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27525,10 +27525,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>131259944</v>
+        <v>131260113</v>
       </c>
       <c r="B240" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27536,39 +27536,34 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>394171</v>
+        <v>394112</v>
       </c>
       <c r="R240" t="n">
-        <v>6951274</v>
+        <v>6951132</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27627,10 +27622,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>131260113</v>
+        <v>131259944</v>
       </c>
       <c r="B241" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27638,34 +27633,39 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P241" t="inlineStr">
         <is>
           <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>394112</v>
+        <v>394171</v>
       </c>
       <c r="R241" t="n">
-        <v>6951132</v>
+        <v>6951274</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27727,7 +27727,7 @@
         <v>131259465</v>
       </c>
       <c r="B242" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>131259470</v>
       </c>
       <c r="B243" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>131260119</v>
       </c>
       <c r="B244" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>131258863</v>
       </c>
       <c r="B245" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>131260370</v>
       </c>
       <c r="B246" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>131258822</v>
       </c>
       <c r="B247" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>131257896</v>
       </c>
       <c r="B248" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28444,10 +28444,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>131260485</v>
+        <v>131260664</v>
       </c>
       <c r="B249" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28484,10 +28484,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>393966</v>
+        <v>393848</v>
       </c>
       <c r="R249" t="n">
-        <v>6950847</v>
+        <v>6950708</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>2 bild, högstubbe</t>
+          <t>1 bild, tydliga hackhål</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28551,10 +28551,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>131260664</v>
+        <v>131260485</v>
       </c>
       <c r="B250" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28591,10 +28591,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>393848</v>
+        <v>393966</v>
       </c>
       <c r="R250" t="n">
-        <v>6950708</v>
+        <v>6950847</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28631,7 +28631,7 @@
       </c>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>1 bild, tydliga hackhål</t>
+          <t>2 bild, högstubbe</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28661,7 +28661,7 @@
         <v>131258260</v>
       </c>
       <c r="B251" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
@@ -28775,7 +28775,7 @@
         <v>131258022</v>
       </c>
       <c r="B252" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>131259617</v>
       </c>
       <c r="B253" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
         <v>131260677</v>
       </c>
       <c r="B254" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>131257444</v>
       </c>
       <c r="B255" t="n">
-        <v>57996</v>
+        <v>58002</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
@@ -29198,7 +29198,7 @@
         <v>131259825</v>
       </c>
       <c r="B256" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>131257828</v>
       </c>
       <c r="B257" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>131260600</v>
       </c>
       <c r="B258" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -26042,10 +26042,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>131260234</v>
+        <v>131259760</v>
       </c>
       <c r="B225" t="n">
-        <v>57898</v>
+        <v>83240</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26053,39 +26053,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>394049</v>
+        <v>394099</v>
       </c>
       <c r="R225" t="n">
-        <v>6951150</v>
+        <v>6951193</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26144,10 +26139,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>131259760</v>
+        <v>131260234</v>
       </c>
       <c r="B226" t="n">
-        <v>83240</v>
+        <v>57898</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26155,34 +26150,39 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>394099</v>
+        <v>394049</v>
       </c>
       <c r="R226" t="n">
-        <v>6951193</v>
+        <v>6951150</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26241,10 +26241,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>131259451</v>
+        <v>131259701</v>
       </c>
       <c r="B227" t="n">
-        <v>91848</v>
+        <v>57898</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26252,30 +26252,39 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>393972</v>
+        <v>394058</v>
       </c>
       <c r="R227" t="n">
-        <v>6951237</v>
+        <v>6951183</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26334,10 +26343,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>131257647</v>
+        <v>131258105</v>
       </c>
       <c r="B228" t="n">
-        <v>83240</v>
+        <v>57898</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26345,34 +26354,39 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>393444</v>
+        <v>393564</v>
       </c>
       <c r="R228" t="n">
-        <v>6951119</v>
+        <v>6950996</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26431,10 +26445,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>131259701</v>
+        <v>131257647</v>
       </c>
       <c r="B229" t="n">
-        <v>57898</v>
+        <v>83240</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26442,39 +26456,34 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>394058</v>
+        <v>393444</v>
       </c>
       <c r="R229" t="n">
-        <v>6951183</v>
+        <v>6951119</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26533,10 +26542,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>131258105</v>
+        <v>131259451</v>
       </c>
       <c r="B230" t="n">
-        <v>57898</v>
+        <v>91848</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26544,39 +26553,30 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>393564</v>
+        <v>393972</v>
       </c>
       <c r="R230" t="n">
-        <v>6950996</v>
+        <v>6951237</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -28137,10 +28137,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>131260370</v>
+        <v>131257896</v>
       </c>
       <c r="B246" t="n">
-        <v>57898</v>
+        <v>91848</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28148,39 +28148,30 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>394001</v>
+        <v>393554</v>
       </c>
       <c r="R246" t="n">
-        <v>6950899</v>
+        <v>6951144</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28215,11 +28206,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>2 bild, tall, rikligt</t>
-        </is>
-      </c>
       <c r="AD246" t="b">
         <v>0</v>
       </c>
@@ -28237,17 +28223,17 @@
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>131258822</v>
+        <v>131260664</v>
       </c>
       <c r="B247" t="n">
-        <v>57898</v>
+        <v>57895</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28255,16 +28241,16 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -28275,7 +28261,7 @@
       <c r="I247" t="inlineStr"/>
       <c r="M247" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
@@ -28284,10 +28270,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>393926</v>
+        <v>393848</v>
       </c>
       <c r="R247" t="n">
-        <v>6951116</v>
+        <v>6950708</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28324,7 +28310,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>1 bild, gran</t>
+          <t>1 bild, tydliga hackhål</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28344,17 +28330,17 @@
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>131257896</v>
+        <v>131260485</v>
       </c>
       <c r="B248" t="n">
-        <v>91848</v>
+        <v>57895</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28362,30 +28348,39 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>393554</v>
+        <v>393966</v>
       </c>
       <c r="R248" t="n">
-        <v>6951144</v>
+        <v>6950847</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28420,6 +28415,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>2 bild, högstubbe</t>
+        </is>
+      </c>
       <c r="AD248" t="b">
         <v>0</v>
       </c>
@@ -28437,17 +28437,17 @@
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>131260664</v>
+        <v>131260370</v>
       </c>
       <c r="B249" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28455,16 +28455,16 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -28484,10 +28484,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>393848</v>
+        <v>394001</v>
       </c>
       <c r="R249" t="n">
-        <v>6950708</v>
+        <v>6950899</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>1 bild, tydliga hackhål</t>
+          <t>2 bild, tall, rikligt</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28551,10 +28551,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>131260485</v>
+        <v>131258822</v>
       </c>
       <c r="B250" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28562,16 +28562,16 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -28582,7 +28582,7 @@
       <c r="I250" t="inlineStr"/>
       <c r="M250" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
@@ -28591,10 +28591,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>393966</v>
+        <v>393926</v>
       </c>
       <c r="R250" t="n">
-        <v>6950847</v>
+        <v>6951116</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28631,7 +28631,7 @@
       </c>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>2 bild, högstubbe</t>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28651,7 +28651,7 @@
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -26241,10 +26241,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>131259701</v>
+        <v>131257647</v>
       </c>
       <c r="B227" t="n">
-        <v>57898</v>
+        <v>83240</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26252,39 +26252,34 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>394058</v>
+        <v>393444</v>
       </c>
       <c r="R227" t="n">
-        <v>6951183</v>
+        <v>6951119</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26343,10 +26338,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>131258105</v>
+        <v>131259451</v>
       </c>
       <c r="B228" t="n">
-        <v>57898</v>
+        <v>91848</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26354,39 +26349,30 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>393564</v>
+        <v>393972</v>
       </c>
       <c r="R228" t="n">
-        <v>6950996</v>
+        <v>6951237</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26445,10 +26431,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>131257647</v>
+        <v>131259701</v>
       </c>
       <c r="B229" t="n">
-        <v>83240</v>
+        <v>57898</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26456,34 +26442,39 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>393444</v>
+        <v>394058</v>
       </c>
       <c r="R229" t="n">
-        <v>6951119</v>
+        <v>6951183</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26542,10 +26533,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>131259451</v>
+        <v>131258105</v>
       </c>
       <c r="B230" t="n">
-        <v>91848</v>
+        <v>57898</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26553,30 +26544,39 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>393972</v>
+        <v>393564</v>
       </c>
       <c r="R230" t="n">
-        <v>6951237</v>
+        <v>6950996</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -27039,45 +27039,45 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>131259937</v>
+        <v>131257698</v>
       </c>
       <c r="B235" t="n">
-        <v>83225</v>
+        <v>79260</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>394158</v>
+        <v>393501</v>
       </c>
       <c r="R235" t="n">
-        <v>6951255</v>
+        <v>6951126</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27124,22 +27124,22 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>131258127</v>
+        <v>131260680</v>
       </c>
       <c r="B236" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27147,30 +27147,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>393574</v>
+        <v>393848</v>
       </c>
       <c r="R236" t="n">
-        <v>6950991</v>
+        <v>6950708</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27217,22 +27221,22 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>131257698</v>
+        <v>131258127</v>
       </c>
       <c r="B237" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27240,34 +27244,30 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>393501</v>
+        <v>393574</v>
       </c>
       <c r="R237" t="n">
-        <v>6951126</v>
+        <v>6950991</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27314,57 +27314,57 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>131260680</v>
+        <v>131259937</v>
       </c>
       <c r="B238" t="n">
-        <v>79260</v>
+        <v>83225</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>393848</v>
+        <v>394158</v>
       </c>
       <c r="R238" t="n">
-        <v>6950708</v>
+        <v>6951255</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27411,12 +27411,12 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
@@ -29093,27 +29093,27 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>131257444</v>
+        <v>131259825</v>
       </c>
       <c r="B255" t="n">
-        <v>58002</v>
+        <v>57898</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -29124,7 +29124,7 @@
       <c r="I255" t="inlineStr"/>
       <c r="M255" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
@@ -29133,10 +29133,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>393426</v>
+        <v>393904</v>
       </c>
       <c r="R255" t="n">
-        <v>6951191</v>
+        <v>6950987</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29171,6 +29171,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
+        </is>
+      </c>
       <c r="AD255" t="b">
         <v>0</v>
       </c>
@@ -29188,34 +29193,34 @@
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>131259825</v>
+        <v>131257444</v>
       </c>
       <c r="B256" t="n">
-        <v>57898</v>
+        <v>58002</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -29226,7 +29231,7 @@
       <c r="I256" t="inlineStr"/>
       <c r="M256" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
@@ -29235,10 +29240,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>393904</v>
+        <v>393426</v>
       </c>
       <c r="R256" t="n">
-        <v>6950987</v>
+        <v>6951191</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -29271,11 +29276,6 @@
       <c r="AA256" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD256" t="b">

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -27039,45 +27039,45 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>131257698</v>
+        <v>131259937</v>
       </c>
       <c r="B235" t="n">
-        <v>79260</v>
+        <v>83225</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>393501</v>
+        <v>394158</v>
       </c>
       <c r="R235" t="n">
-        <v>6951126</v>
+        <v>6951255</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27124,19 +27124,19 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>131260680</v>
+        <v>131257698</v>
       </c>
       <c r="B236" t="n">
         <v>79260</v>
@@ -27171,10 +27171,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>393848</v>
+        <v>393501</v>
       </c>
       <c r="R236" t="n">
-        <v>6950708</v>
+        <v>6951126</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27226,17 +27226,17 @@
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>131258127</v>
+        <v>131260680</v>
       </c>
       <c r="B237" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27244,30 +27244,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>393574</v>
+        <v>393848</v>
       </c>
       <c r="R237" t="n">
-        <v>6950991</v>
+        <v>6950708</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27314,57 +27318,53 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>131259937</v>
+        <v>131258127</v>
       </c>
       <c r="B238" t="n">
-        <v>83225</v>
+        <v>91848</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>306</v>
+        <v>5432</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>394158</v>
+        <v>393574</v>
       </c>
       <c r="R238" t="n">
-        <v>6951255</v>
+        <v>6950991</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -26042,10 +26042,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>131259760</v>
+        <v>131260234</v>
       </c>
       <c r="B225" t="n">
-        <v>83240</v>
+        <v>57898</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26053,34 +26053,39 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>394099</v>
+        <v>394049</v>
       </c>
       <c r="R225" t="n">
-        <v>6951193</v>
+        <v>6951150</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26139,10 +26144,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>131260234</v>
+        <v>131259760</v>
       </c>
       <c r="B226" t="n">
-        <v>57898</v>
+        <v>83240</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26150,39 +26155,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>394049</v>
+        <v>394099</v>
       </c>
       <c r="R226" t="n">
-        <v>6951150</v>
+        <v>6951193</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26241,10 +26241,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>131257647</v>
+        <v>131259451</v>
       </c>
       <c r="B227" t="n">
-        <v>83240</v>
+        <v>91848</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26252,23 +26252,19 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
@@ -26276,10 +26272,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>393444</v>
+        <v>393972</v>
       </c>
       <c r="R227" t="n">
-        <v>6951119</v>
+        <v>6951237</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26338,10 +26334,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>131259451</v>
+        <v>131257647</v>
       </c>
       <c r="B228" t="n">
-        <v>91848</v>
+        <v>83240</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26349,19 +26345,23 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
@@ -26369,10 +26369,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>393972</v>
+        <v>393444</v>
       </c>
       <c r="R228" t="n">
-        <v>6951237</v>
+        <v>6951119</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -27039,45 +27039,45 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>131259937</v>
+        <v>131257698</v>
       </c>
       <c r="B235" t="n">
-        <v>83225</v>
+        <v>79260</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>394158</v>
+        <v>393501</v>
       </c>
       <c r="R235" t="n">
-        <v>6951255</v>
+        <v>6951126</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27124,19 +27124,19 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>131257698</v>
+        <v>131260680</v>
       </c>
       <c r="B236" t="n">
         <v>79260</v>
@@ -27171,10 +27171,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>393501</v>
+        <v>393848</v>
       </c>
       <c r="R236" t="n">
-        <v>6951126</v>
+        <v>6950708</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27226,52 +27226,52 @@
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>131260680</v>
+        <v>131259937</v>
       </c>
       <c r="B237" t="n">
-        <v>79260</v>
+        <v>83225</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>393848</v>
+        <v>394158</v>
       </c>
       <c r="R237" t="n">
-        <v>6950708</v>
+        <v>6951255</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27318,12 +27318,12 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
@@ -28137,10 +28137,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>131257896</v>
+        <v>131260664</v>
       </c>
       <c r="B246" t="n">
-        <v>91848</v>
+        <v>57895</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28148,30 +28148,39 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>393554</v>
+        <v>393848</v>
       </c>
       <c r="R246" t="n">
-        <v>6951144</v>
+        <v>6950708</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28206,6 +28215,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>1 bild, tydliga hackhål</t>
+        </is>
+      </c>
       <c r="AD246" t="b">
         <v>0</v>
       </c>
@@ -28223,14 +28237,14 @@
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>131260664</v>
+        <v>131260485</v>
       </c>
       <c r="B247" t="n">
         <v>57895</v>
@@ -28270,10 +28284,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>393848</v>
+        <v>393966</v>
       </c>
       <c r="R247" t="n">
-        <v>6950708</v>
+        <v>6950847</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28310,7 +28324,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>1 bild, tydliga hackhål</t>
+          <t>2 bild, högstubbe</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28337,10 +28351,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>131260485</v>
+        <v>131260370</v>
       </c>
       <c r="B248" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28348,16 +28362,16 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -28377,10 +28391,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>393966</v>
+        <v>394001</v>
       </c>
       <c r="R248" t="n">
-        <v>6950847</v>
+        <v>6950899</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28417,7 +28431,7 @@
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>2 bild, högstubbe</t>
+          <t>2 bild, tall, rikligt</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28444,7 +28458,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>131260370</v>
+        <v>131258822</v>
       </c>
       <c r="B249" t="n">
         <v>57898</v>
@@ -28475,7 +28489,7 @@
       <c r="I249" t="inlineStr"/>
       <c r="M249" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
@@ -28484,10 +28498,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>394001</v>
+        <v>393926</v>
       </c>
       <c r="R249" t="n">
-        <v>6950899</v>
+        <v>6951116</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28524,7 +28538,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>2 bild, tall, rikligt</t>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28544,17 +28558,17 @@
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>131258822</v>
+        <v>131257896</v>
       </c>
       <c r="B250" t="n">
-        <v>57898</v>
+        <v>91848</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28562,39 +28576,30 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr"/>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P250" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>393926</v>
+        <v>393554</v>
       </c>
       <c r="R250" t="n">
-        <v>6951116</v>
+        <v>6951144</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28627,11 +28632,6 @@
       <c r="AA250" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -29295,7 +29295,7 @@
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -25452,7 +25452,7 @@
         <v>131260454</v>
       </c>
       <c r="B219" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>131258518</v>
       </c>
       <c r="B220" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>131259806</v>
       </c>
       <c r="B221" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25750,10 +25750,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>131257750</v>
+        <v>131259983</v>
       </c>
       <c r="B222" t="n">
-        <v>83240</v>
+        <v>57899</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25761,34 +25761,39 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>393518</v>
+        <v>394187</v>
       </c>
       <c r="R222" t="n">
-        <v>6951114</v>
+        <v>6951218</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25847,10 +25852,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>131259983</v>
+        <v>131257750</v>
       </c>
       <c r="B223" t="n">
-        <v>57898</v>
+        <v>83241</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25858,39 +25863,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>394187</v>
+        <v>393518</v>
       </c>
       <c r="R223" t="n">
-        <v>6951218</v>
+        <v>6951114</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25952,7 +25952,7 @@
         <v>131257777</v>
       </c>
       <c r="B224" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>131260234</v>
       </c>
       <c r="B225" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>131259760</v>
       </c>
       <c r="B226" t="n">
-        <v>83240</v>
+        <v>83241</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26241,10 +26241,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>131259451</v>
+        <v>131259701</v>
       </c>
       <c r="B227" t="n">
-        <v>91848</v>
+        <v>57899</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26252,30 +26252,39 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>393972</v>
+        <v>394058</v>
       </c>
       <c r="R227" t="n">
-        <v>6951237</v>
+        <v>6951183</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26334,10 +26343,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>131257647</v>
+        <v>131258105</v>
       </c>
       <c r="B228" t="n">
-        <v>83240</v>
+        <v>57899</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26345,34 +26354,39 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>393444</v>
+        <v>393564</v>
       </c>
       <c r="R228" t="n">
-        <v>6951119</v>
+        <v>6950996</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26431,10 +26445,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>131259701</v>
+        <v>131259451</v>
       </c>
       <c r="B229" t="n">
-        <v>57898</v>
+        <v>91849</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26442,39 +26456,30 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>394058</v>
+        <v>393972</v>
       </c>
       <c r="R229" t="n">
-        <v>6951183</v>
+        <v>6951237</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26533,10 +26538,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>131258105</v>
+        <v>131257647</v>
       </c>
       <c r="B230" t="n">
-        <v>57898</v>
+        <v>83241</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26544,39 +26549,34 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>393564</v>
+        <v>393444</v>
       </c>
       <c r="R230" t="n">
-        <v>6950996</v>
+        <v>6951119</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26638,7 +26638,7 @@
         <v>131258813</v>
       </c>
       <c r="B231" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>131259721</v>
       </c>
       <c r="B232" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>131260181</v>
       </c>
       <c r="B233" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>131257765</v>
       </c>
       <c r="B234" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27039,10 +27039,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>131257698</v>
+        <v>131258127</v>
       </c>
       <c r="B235" t="n">
-        <v>79260</v>
+        <v>91849</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27050,34 +27050,30 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>393501</v>
+        <v>393574</v>
       </c>
       <c r="R235" t="n">
-        <v>6951126</v>
+        <v>6950991</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27124,22 +27120,22 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>131260680</v>
+        <v>131257698</v>
       </c>
       <c r="B236" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27171,10 +27167,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>393848</v>
+        <v>393501</v>
       </c>
       <c r="R236" t="n">
-        <v>6950708</v>
+        <v>6951126</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27226,52 +27222,52 @@
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>131259937</v>
+        <v>131260680</v>
       </c>
       <c r="B237" t="n">
-        <v>83225</v>
+        <v>79261</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>394158</v>
+        <v>393848</v>
       </c>
       <c r="R237" t="n">
-        <v>6951255</v>
+        <v>6950708</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27318,53 +27314,57 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>131258127</v>
+        <v>131259937</v>
       </c>
       <c r="B238" t="n">
-        <v>91848</v>
+        <v>83226</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>5432</v>
+        <v>306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr"/>
+          <t>Chaenotheca chlorella</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>393574</v>
+        <v>394158</v>
       </c>
       <c r="R238" t="n">
-        <v>6950991</v>
+        <v>6951255</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27426,7 +27426,7 @@
         <v>131258210</v>
       </c>
       <c r="B239" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>131260113</v>
       </c>
       <c r="B240" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>131259944</v>
       </c>
       <c r="B241" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>131259465</v>
       </c>
       <c r="B242" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>131259470</v>
       </c>
       <c r="B243" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>131260119</v>
       </c>
       <c r="B244" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>131258863</v>
       </c>
       <c r="B245" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28137,10 +28137,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>131260664</v>
+        <v>131257896</v>
       </c>
       <c r="B246" t="n">
-        <v>57895</v>
+        <v>91849</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28148,39 +28148,30 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>393848</v>
+        <v>393554</v>
       </c>
       <c r="R246" t="n">
-        <v>6950708</v>
+        <v>6951144</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28215,11 +28206,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>1 bild, tydliga hackhål</t>
-        </is>
-      </c>
       <c r="AD246" t="b">
         <v>0</v>
       </c>
@@ -28237,17 +28223,17 @@
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>131260485</v>
+        <v>131260370</v>
       </c>
       <c r="B247" t="n">
-        <v>57895</v>
+        <v>57899</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28255,16 +28241,16 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -28284,10 +28270,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>393966</v>
+        <v>394001</v>
       </c>
       <c r="R247" t="n">
-        <v>6950847</v>
+        <v>6950899</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28324,7 +28310,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>2 bild, högstubbe</t>
+          <t>2 bild, tall, rikligt</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28351,10 +28337,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>131260370</v>
+        <v>131258822</v>
       </c>
       <c r="B248" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28382,7 +28368,7 @@
       <c r="I248" t="inlineStr"/>
       <c r="M248" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
@@ -28391,10 +28377,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>394001</v>
+        <v>393926</v>
       </c>
       <c r="R248" t="n">
-        <v>6950899</v>
+        <v>6951116</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28431,7 +28417,7 @@
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>2 bild, tall, rikligt</t>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28451,17 +28437,17 @@
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>131258822</v>
+        <v>131260664</v>
       </c>
       <c r="B249" t="n">
-        <v>57898</v>
+        <v>57896</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28469,16 +28455,16 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -28489,7 +28475,7 @@
       <c r="I249" t="inlineStr"/>
       <c r="M249" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
@@ -28498,10 +28484,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>393926</v>
+        <v>393848</v>
       </c>
       <c r="R249" t="n">
-        <v>6951116</v>
+        <v>6950708</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28538,7 +28524,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>1 bild, gran</t>
+          <t>1 bild, tydliga hackhål</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28558,17 +28544,17 @@
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>131257896</v>
+        <v>131260485</v>
       </c>
       <c r="B250" t="n">
-        <v>91848</v>
+        <v>57896</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28576,30 +28562,39 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P250" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>393554</v>
+        <v>393966</v>
       </c>
       <c r="R250" t="n">
-        <v>6951144</v>
+        <v>6950847</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28634,6 +28629,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>2 bild, högstubbe</t>
+        </is>
+      </c>
       <c r="AD250" t="b">
         <v>0</v>
       </c>
@@ -28651,7 +28651,7 @@
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
@@ -28661,7 +28661,7 @@
         <v>131258260</v>
       </c>
       <c r="B251" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>131258022</v>
       </c>
       <c r="B252" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>131259617</v>
       </c>
       <c r="B253" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
         <v>131260677</v>
       </c>
       <c r="B254" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>131259825</v>
       </c>
       <c r="B255" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>131257444</v>
       </c>
       <c r="B256" t="n">
-        <v>58002</v>
+        <v>58003</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
@@ -29305,7 +29305,7 @@
         <v>131257828</v>
       </c>
       <c r="B257" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>131260600</v>
       </c>
       <c r="B258" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -25452,7 +25452,7 @@
         <v>131260454</v>
       </c>
       <c r="B219" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>131258518</v>
       </c>
       <c r="B220" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>131259806</v>
       </c>
       <c r="B221" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>131259983</v>
       </c>
       <c r="B222" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>131257750</v>
       </c>
       <c r="B223" t="n">
-        <v>83241</v>
+        <v>83244</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>131257777</v>
       </c>
       <c r="B224" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>131260234</v>
       </c>
       <c r="B225" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>131259760</v>
       </c>
       <c r="B226" t="n">
-        <v>83241</v>
+        <v>83244</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>131259701</v>
       </c>
       <c r="B227" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>131258105</v>
       </c>
       <c r="B228" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26445,10 +26445,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>131259451</v>
+        <v>131257647</v>
       </c>
       <c r="B229" t="n">
-        <v>91849</v>
+        <v>83244</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26456,19 +26456,23 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
@@ -26476,10 +26480,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>393972</v>
+        <v>393444</v>
       </c>
       <c r="R229" t="n">
-        <v>6951237</v>
+        <v>6951119</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26538,10 +26542,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>131257647</v>
+        <v>131259451</v>
       </c>
       <c r="B230" t="n">
-        <v>83241</v>
+        <v>91852</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26549,23 +26553,19 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
@@ -26573,10 +26573,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>393444</v>
+        <v>393972</v>
       </c>
       <c r="R230" t="n">
-        <v>6951119</v>
+        <v>6951237</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26638,7 +26638,7 @@
         <v>131258813</v>
       </c>
       <c r="B231" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>131259721</v>
       </c>
       <c r="B232" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>131260181</v>
       </c>
       <c r="B233" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>131257765</v>
       </c>
       <c r="B234" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27039,41 +27039,45 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>131258127</v>
+        <v>131259937</v>
       </c>
       <c r="B235" t="n">
-        <v>91849</v>
+        <v>83229</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>5432</v>
+        <v>306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr"/>
+          <t>Chaenotheca chlorella</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>393574</v>
+        <v>394158</v>
       </c>
       <c r="R235" t="n">
-        <v>6950991</v>
+        <v>6951255</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27135,7 +27139,7 @@
         <v>131257698</v>
       </c>
       <c r="B236" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27232,7 +27236,7 @@
         <v>131260680</v>
       </c>
       <c r="B237" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27326,45 +27330,41 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>131259937</v>
+        <v>131258127</v>
       </c>
       <c r="B238" t="n">
-        <v>83226</v>
+        <v>91852</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>306</v>
+        <v>5432</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>394158</v>
+        <v>393574</v>
       </c>
       <c r="R238" t="n">
-        <v>6951255</v>
+        <v>6950991</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27426,7 +27426,7 @@
         <v>131258210</v>
       </c>
       <c r="B239" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>131260113</v>
       </c>
       <c r="B240" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>131259944</v>
       </c>
       <c r="B241" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27724,10 +27724,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>131259465</v>
+        <v>131259470</v>
       </c>
       <c r="B242" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27735,24 +27735,29 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P242" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
@@ -27821,10 +27826,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>131259470</v>
+        <v>131259465</v>
       </c>
       <c r="B243" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27832,29 +27837,24 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
@@ -27926,7 +27926,7 @@
         <v>131260119</v>
       </c>
       <c r="B244" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>131258863</v>
       </c>
       <c r="B245" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28137,10 +28137,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>131257896</v>
+        <v>131260664</v>
       </c>
       <c r="B246" t="n">
-        <v>91849</v>
+        <v>57899</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28148,30 +28148,39 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>393554</v>
+        <v>393848</v>
       </c>
       <c r="R246" t="n">
-        <v>6951144</v>
+        <v>6950708</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28206,6 +28215,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>1 bild, tydliga hackhål</t>
+        </is>
+      </c>
       <c r="AD246" t="b">
         <v>0</v>
       </c>
@@ -28223,14 +28237,14 @@
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>131260370</v>
+        <v>131260485</v>
       </c>
       <c r="B247" t="n">
         <v>57899</v>
@@ -28241,16 +28255,16 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -28270,10 +28284,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>394001</v>
+        <v>393966</v>
       </c>
       <c r="R247" t="n">
-        <v>6950899</v>
+        <v>6950847</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28310,7 +28324,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>2 bild, tall, rikligt</t>
+          <t>2 bild, högstubbe</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28337,10 +28351,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>131258822</v>
+        <v>131260370</v>
       </c>
       <c r="B248" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28368,7 +28382,7 @@
       <c r="I248" t="inlineStr"/>
       <c r="M248" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
@@ -28377,10 +28391,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>393926</v>
+        <v>394001</v>
       </c>
       <c r="R248" t="n">
-        <v>6951116</v>
+        <v>6950899</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28417,7 +28431,7 @@
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>1 bild, gran</t>
+          <t>2 bild, tall, rikligt</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28437,17 +28451,17 @@
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>131260664</v>
+        <v>131258822</v>
       </c>
       <c r="B249" t="n">
-        <v>57896</v>
+        <v>57902</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28455,16 +28469,16 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -28475,7 +28489,7 @@
       <c r="I249" t="inlineStr"/>
       <c r="M249" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
@@ -28484,10 +28498,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>393848</v>
+        <v>393926</v>
       </c>
       <c r="R249" t="n">
-        <v>6950708</v>
+        <v>6951116</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28524,7 +28538,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>1 bild, tydliga hackhål</t>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28544,17 +28558,17 @@
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>131260485</v>
+        <v>131257896</v>
       </c>
       <c r="B250" t="n">
-        <v>57896</v>
+        <v>91852</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28562,39 +28576,30 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr"/>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P250" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>393966</v>
+        <v>393554</v>
       </c>
       <c r="R250" t="n">
-        <v>6950847</v>
+        <v>6951144</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28629,11 +28634,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>2 bild, högstubbe</t>
-        </is>
-      </c>
       <c r="AD250" t="b">
         <v>0</v>
       </c>
@@ -28651,7 +28651,7 @@
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
@@ -28661,7 +28661,7 @@
         <v>131258260</v>
       </c>
       <c r="B251" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>131258022</v>
       </c>
       <c r="B252" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>131259617</v>
       </c>
       <c r="B253" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
         <v>131260677</v>
       </c>
       <c r="B254" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>131259825</v>
       </c>
       <c r="B255" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>131257444</v>
       </c>
       <c r="B256" t="n">
-        <v>58003</v>
+        <v>58006</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>131257828</v>
       </c>
       <c r="B257" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>131260600</v>
       </c>
       <c r="B258" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -25750,10 +25750,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>131259983</v>
+        <v>131257750</v>
       </c>
       <c r="B222" t="n">
-        <v>57902</v>
+        <v>83244</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25761,39 +25761,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>394187</v>
+        <v>393518</v>
       </c>
       <c r="R222" t="n">
-        <v>6951218</v>
+        <v>6951114</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25852,10 +25847,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>131257750</v>
+        <v>131259983</v>
       </c>
       <c r="B223" t="n">
-        <v>83244</v>
+        <v>57902</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25863,34 +25858,39 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>393518</v>
+        <v>394187</v>
       </c>
       <c r="R223" t="n">
-        <v>6951114</v>
+        <v>6951218</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -26042,10 +26042,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>131260234</v>
+        <v>131259760</v>
       </c>
       <c r="B225" t="n">
-        <v>57902</v>
+        <v>83244</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26053,39 +26053,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>394049</v>
+        <v>394099</v>
       </c>
       <c r="R225" t="n">
-        <v>6951150</v>
+        <v>6951193</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26144,10 +26139,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>131259760</v>
+        <v>131260234</v>
       </c>
       <c r="B226" t="n">
-        <v>83244</v>
+        <v>57902</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26155,34 +26150,39 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>394099</v>
+        <v>394049</v>
       </c>
       <c r="R226" t="n">
-        <v>6951193</v>
+        <v>6951150</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26241,7 +26241,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>131259701</v>
+        <v>131258105</v>
       </c>
       <c r="B227" t="n">
         <v>57902</v>
@@ -26277,14 +26277,14 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>394058</v>
+        <v>393564</v>
       </c>
       <c r="R227" t="n">
-        <v>6951183</v>
+        <v>6950996</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26343,7 +26343,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>131258105</v>
+        <v>131259701</v>
       </c>
       <c r="B228" t="n">
         <v>57902</v>
@@ -26379,14 +26379,14 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>393564</v>
+        <v>394058</v>
       </c>
       <c r="R228" t="n">
-        <v>6950996</v>
+        <v>6951183</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26445,10 +26445,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>131257647</v>
+        <v>131259451</v>
       </c>
       <c r="B229" t="n">
-        <v>83244</v>
+        <v>91852</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26456,23 +26456,19 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
@@ -26480,10 +26476,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>393444</v>
+        <v>393972</v>
       </c>
       <c r="R229" t="n">
-        <v>6951119</v>
+        <v>6951237</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26542,10 +26538,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>131259451</v>
+        <v>131257647</v>
       </c>
       <c r="B230" t="n">
-        <v>91852</v>
+        <v>83244</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26553,19 +26549,23 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
@@ -26573,10 +26573,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>393972</v>
+        <v>393444</v>
       </c>
       <c r="R230" t="n">
-        <v>6951237</v>
+        <v>6951119</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -27039,45 +27039,45 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>131259937</v>
+        <v>131257698</v>
       </c>
       <c r="B235" t="n">
-        <v>83229</v>
+        <v>79264</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>394158</v>
+        <v>393501</v>
       </c>
       <c r="R235" t="n">
-        <v>6951255</v>
+        <v>6951126</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27124,19 +27124,19 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>131257698</v>
+        <v>131260680</v>
       </c>
       <c r="B236" t="n">
         <v>79264</v>
@@ -27171,10 +27171,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>393501</v>
+        <v>393848</v>
       </c>
       <c r="R236" t="n">
-        <v>6951126</v>
+        <v>6950708</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27226,17 +27226,17 @@
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>131260680</v>
+        <v>131258127</v>
       </c>
       <c r="B237" t="n">
-        <v>79264</v>
+        <v>91852</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27244,34 +27244,30 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>393848</v>
+        <v>393574</v>
       </c>
       <c r="R237" t="n">
-        <v>6950708</v>
+        <v>6950991</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27318,53 +27314,57 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>131258127</v>
+        <v>131259937</v>
       </c>
       <c r="B238" t="n">
-        <v>91852</v>
+        <v>83229</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>5432</v>
+        <v>306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr"/>
+          <t>Chaenotheca chlorella</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>393574</v>
+        <v>394158</v>
       </c>
       <c r="R238" t="n">
-        <v>6950991</v>
+        <v>6951255</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -28137,10 +28137,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>131260664</v>
+        <v>131257896</v>
       </c>
       <c r="B246" t="n">
-        <v>57899</v>
+        <v>91852</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28148,39 +28148,30 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>393848</v>
+        <v>393554</v>
       </c>
       <c r="R246" t="n">
-        <v>6950708</v>
+        <v>6951144</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28215,11 +28206,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>1 bild, tydliga hackhål</t>
-        </is>
-      </c>
       <c r="AD246" t="b">
         <v>0</v>
       </c>
@@ -28237,17 +28223,17 @@
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>131260485</v>
+        <v>131260370</v>
       </c>
       <c r="B247" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28255,16 +28241,16 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -28284,10 +28270,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>393966</v>
+        <v>394001</v>
       </c>
       <c r="R247" t="n">
-        <v>6950847</v>
+        <v>6950899</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28324,7 +28310,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>2 bild, högstubbe</t>
+          <t>2 bild, tall, rikligt</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28351,7 +28337,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>131260370</v>
+        <v>131258822</v>
       </c>
       <c r="B248" t="n">
         <v>57902</v>
@@ -28382,7 +28368,7 @@
       <c r="I248" t="inlineStr"/>
       <c r="M248" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
@@ -28391,10 +28377,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>394001</v>
+        <v>393926</v>
       </c>
       <c r="R248" t="n">
-        <v>6950899</v>
+        <v>6951116</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28431,7 +28417,7 @@
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>2 bild, tall, rikligt</t>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28451,17 +28437,17 @@
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>131258822</v>
+        <v>131260664</v>
       </c>
       <c r="B249" t="n">
-        <v>57902</v>
+        <v>57899</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28469,16 +28455,16 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -28489,7 +28475,7 @@
       <c r="I249" t="inlineStr"/>
       <c r="M249" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
@@ -28498,10 +28484,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>393926</v>
+        <v>393848</v>
       </c>
       <c r="R249" t="n">
-        <v>6951116</v>
+        <v>6950708</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28538,7 +28524,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>1 bild, gran</t>
+          <t>1 bild, tydliga hackhål</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28558,17 +28544,17 @@
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>131257896</v>
+        <v>131260485</v>
       </c>
       <c r="B250" t="n">
-        <v>91852</v>
+        <v>57899</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28576,30 +28562,39 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P250" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>393554</v>
+        <v>393966</v>
       </c>
       <c r="R250" t="n">
-        <v>6951144</v>
+        <v>6950847</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28634,6 +28629,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>2 bild, högstubbe</t>
+        </is>
+      </c>
       <c r="AD250" t="b">
         <v>0</v>
       </c>
@@ -28651,7 +28651,7 @@
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
@@ -29093,27 +29093,27 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>131259825</v>
+        <v>131257444</v>
       </c>
       <c r="B255" t="n">
-        <v>57902</v>
+        <v>58006</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -29124,7 +29124,7 @@
       <c r="I255" t="inlineStr"/>
       <c r="M255" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
@@ -29133,10 +29133,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>393904</v>
+        <v>393426</v>
       </c>
       <c r="R255" t="n">
-        <v>6950987</v>
+        <v>6951191</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29169,11 +29169,6 @@
       <c r="AA255" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29200,27 +29195,27 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>131257444</v>
+        <v>131259825</v>
       </c>
       <c r="B256" t="n">
-        <v>58006</v>
+        <v>57902</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -29231,7 +29226,7 @@
       <c r="I256" t="inlineStr"/>
       <c r="M256" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
@@ -29240,10 +29235,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>393426</v>
+        <v>393904</v>
       </c>
       <c r="R256" t="n">
-        <v>6951191</v>
+        <v>6950987</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -29276,6 +29271,11 @@
       <c r="AA256" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD256" t="b">

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -26241,7 +26241,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>131258105</v>
+        <v>131259701</v>
       </c>
       <c r="B227" t="n">
         <v>57902</v>
@@ -26277,14 +26277,14 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>393564</v>
+        <v>394058</v>
       </c>
       <c r="R227" t="n">
-        <v>6950996</v>
+        <v>6951183</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26343,7 +26343,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>131259701</v>
+        <v>131258105</v>
       </c>
       <c r="B228" t="n">
         <v>57902</v>
@@ -26379,14 +26379,14 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>394058</v>
+        <v>393564</v>
       </c>
       <c r="R228" t="n">
-        <v>6951183</v>
+        <v>6950996</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26445,10 +26445,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>131259451</v>
+        <v>131257647</v>
       </c>
       <c r="B229" t="n">
-        <v>91852</v>
+        <v>83244</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26456,19 +26456,23 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
@@ -26476,10 +26480,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>393972</v>
+        <v>393444</v>
       </c>
       <c r="R229" t="n">
-        <v>6951237</v>
+        <v>6951119</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26538,10 +26542,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>131257647</v>
+        <v>131259451</v>
       </c>
       <c r="B230" t="n">
-        <v>83244</v>
+        <v>91852</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26549,23 +26553,19 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
@@ -26573,10 +26573,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>393444</v>
+        <v>393972</v>
       </c>
       <c r="R230" t="n">
-        <v>6951119</v>
+        <v>6951237</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -27039,45 +27039,45 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>131257698</v>
+        <v>131259937</v>
       </c>
       <c r="B235" t="n">
-        <v>79264</v>
+        <v>83229</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>SO Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>393501</v>
+        <v>394158</v>
       </c>
       <c r="R235" t="n">
-        <v>6951126</v>
+        <v>6951255</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27124,12 +27124,12 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
@@ -27233,10 +27233,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>131258127</v>
+        <v>131257698</v>
       </c>
       <c r="B237" t="n">
-        <v>91852</v>
+        <v>79264</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27244,30 +27244,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>S om Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>393574</v>
+        <v>393501</v>
       </c>
       <c r="R237" t="n">
-        <v>6950991</v>
+        <v>6951126</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27314,57 +27318,53 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>131259937</v>
+        <v>131258127</v>
       </c>
       <c r="B238" t="n">
-        <v>83229</v>
+        <v>91852</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>306</v>
+        <v>5432</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>SO Ruvallen, Hjd</t>
+          <t>S om Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>394158</v>
+        <v>393574</v>
       </c>
       <c r="R238" t="n">
-        <v>6951255</v>
+        <v>6950991</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27724,10 +27724,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>131259470</v>
+        <v>131259465</v>
       </c>
       <c r="B242" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27735,29 +27735,24 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P242" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
@@ -27826,10 +27821,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>131259465</v>
+        <v>131259470</v>
       </c>
       <c r="B243" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27837,24 +27832,29 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>S om Ruvallen, Hjd</t>
@@ -28137,10 +28137,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>131257896</v>
+        <v>131260370</v>
       </c>
       <c r="B246" t="n">
-        <v>91852</v>
+        <v>57902</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28148,30 +28148,39 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>393554</v>
+        <v>394001</v>
       </c>
       <c r="R246" t="n">
-        <v>6951144</v>
+        <v>6950899</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28206,6 +28215,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>2 bild, tall, rikligt</t>
+        </is>
+      </c>
       <c r="AD246" t="b">
         <v>0</v>
       </c>
@@ -28223,14 +28237,14 @@
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>131260370</v>
+        <v>131258822</v>
       </c>
       <c r="B247" t="n">
         <v>57902</v>
@@ -28261,7 +28275,7 @@
       <c r="I247" t="inlineStr"/>
       <c r="M247" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
@@ -28270,10 +28284,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>394001</v>
+        <v>393926</v>
       </c>
       <c r="R247" t="n">
-        <v>6950899</v>
+        <v>6951116</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28310,7 +28324,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>2 bild, tall, rikligt</t>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28330,17 +28344,17 @@
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>131258822</v>
+        <v>131257896</v>
       </c>
       <c r="B248" t="n">
-        <v>57902</v>
+        <v>91852</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28348,39 +28362,30 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr"/>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>393926</v>
+        <v>393554</v>
       </c>
       <c r="R248" t="n">
-        <v>6951116</v>
+        <v>6951144</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28413,11 +28418,6 @@
       <c r="AA248" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -29093,27 +29093,27 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>131257444</v>
+        <v>131259825</v>
       </c>
       <c r="B255" t="n">
-        <v>58006</v>
+        <v>57902</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -29124,7 +29124,7 @@
       <c r="I255" t="inlineStr"/>
       <c r="M255" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
@@ -29133,10 +29133,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>393426</v>
+        <v>393904</v>
       </c>
       <c r="R255" t="n">
-        <v>6951191</v>
+        <v>6950987</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29169,6 +29169,11 @@
       <c r="AA255" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29195,27 +29200,27 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>131259825</v>
+        <v>131257444</v>
       </c>
       <c r="B256" t="n">
-        <v>57902</v>
+        <v>58006</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -29226,7 +29231,7 @@
       <c r="I256" t="inlineStr"/>
       <c r="M256" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
@@ -29235,10 +29240,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>393904</v>
+        <v>393426</v>
       </c>
       <c r="R256" t="n">
-        <v>6950987</v>
+        <v>6951191</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -29271,11 +29276,6 @@
       <c r="AA256" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD256" t="b">

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -27926,7 +27926,7 @@
         <v>131260119</v>
       </c>
       <c r="B244" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>131258863</v>
       </c>
       <c r="B245" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28137,10 +28137,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>131260370</v>
+        <v>131257896</v>
       </c>
       <c r="B246" t="n">
-        <v>57902</v>
+        <v>91858</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28148,39 +28148,30 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>394001</v>
+        <v>393554</v>
       </c>
       <c r="R246" t="n">
-        <v>6950899</v>
+        <v>6951144</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28215,11 +28206,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>2 bild, tall, rikligt</t>
-        </is>
-      </c>
       <c r="AD246" t="b">
         <v>0</v>
       </c>
@@ -28237,17 +28223,17 @@
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>131258822</v>
+        <v>131260370</v>
       </c>
       <c r="B247" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28275,7 +28261,7 @@
       <c r="I247" t="inlineStr"/>
       <c r="M247" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
@@ -28284,10 +28270,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>393926</v>
+        <v>394001</v>
       </c>
       <c r="R247" t="n">
-        <v>6951116</v>
+        <v>6950899</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28324,7 +28310,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>1 bild, gran</t>
+          <t>2 bild, tall, rikligt</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28344,17 +28330,17 @@
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>131257896</v>
+        <v>131258822</v>
       </c>
       <c r="B248" t="n">
-        <v>91852</v>
+        <v>57904</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28362,30 +28348,39 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>393554</v>
+        <v>393926</v>
       </c>
       <c r="R248" t="n">
-        <v>6951144</v>
+        <v>6951116</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28418,6 +28413,11 @@
       <c r="AA248" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28447,7 +28447,7 @@
         <v>131260664</v>
       </c>
       <c r="B249" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>131260485</v>
       </c>
       <c r="B250" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>131258260</v>
       </c>
       <c r="B251" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>131258022</v>
       </c>
       <c r="B252" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>131259617</v>
       </c>
       <c r="B253" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
         <v>131260677</v>
       </c>
       <c r="B254" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>131259825</v>
       </c>
       <c r="B255" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>131257444</v>
       </c>
       <c r="B256" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>131257828</v>
       </c>
       <c r="B257" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>131260600</v>
       </c>
       <c r="B258" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -29093,27 +29093,27 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>131259825</v>
+        <v>131257444</v>
       </c>
       <c r="B255" t="n">
-        <v>57904</v>
+        <v>58008</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -29124,7 +29124,7 @@
       <c r="I255" t="inlineStr"/>
       <c r="M255" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
@@ -29133,10 +29133,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>393904</v>
+        <v>393426</v>
       </c>
       <c r="R255" t="n">
-        <v>6950987</v>
+        <v>6951191</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29169,11 +29169,6 @@
       <c r="AA255" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29200,27 +29195,27 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>131257444</v>
+        <v>131259825</v>
       </c>
       <c r="B256" t="n">
-        <v>58008</v>
+        <v>57904</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -29231,7 +29226,7 @@
       <c r="I256" t="inlineStr"/>
       <c r="M256" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
@@ -29240,10 +29235,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>393426</v>
+        <v>393904</v>
       </c>
       <c r="R256" t="n">
-        <v>6951191</v>
+        <v>6950987</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -29276,6 +29271,11 @@
       <c r="AA256" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD256" t="b">

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -29093,27 +29093,27 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>131257444</v>
+        <v>131259825</v>
       </c>
       <c r="B255" t="n">
-        <v>58008</v>
+        <v>57904</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -29124,7 +29124,7 @@
       <c r="I255" t="inlineStr"/>
       <c r="M255" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
@@ -29133,10 +29133,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>393426</v>
+        <v>393904</v>
       </c>
       <c r="R255" t="n">
-        <v>6951191</v>
+        <v>6950987</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29169,6 +29169,11 @@
       <c r="AA255" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29195,27 +29200,27 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>131259825</v>
+        <v>131257444</v>
       </c>
       <c r="B256" t="n">
-        <v>57904</v>
+        <v>58008</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -29226,7 +29231,7 @@
       <c r="I256" t="inlineStr"/>
       <c r="M256" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
@@ -29235,10 +29240,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>393904</v>
+        <v>393426</v>
       </c>
       <c r="R256" t="n">
-        <v>6950987</v>
+        <v>6951191</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -29271,11 +29276,6 @@
       <c r="AA256" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD256" t="b">

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY237"/>
+  <dimension ref="A1:AZ237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286576</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375202</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131259937</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286622</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86274466</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286592</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287059</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1464,6 +1504,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287060</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1569,6 +1614,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86289111</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1671,6 +1721,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131258545</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1768,6 +1823,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286596</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1865,6 +1925,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286597</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1962,6 +2027,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286598</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2059,6 +2129,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286599</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2156,6 +2231,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286600</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2253,6 +2333,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287064</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2350,6 +2435,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375254</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2447,6 +2537,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287056</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2544,6 +2639,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375253</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2646,6 +2746,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375204</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2747,6 +2852,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76941663</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2848,6 +2958,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76941675</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2949,6 +3064,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76941727</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3046,6 +3166,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286578</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3143,6 +3268,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286579</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3240,6 +3370,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286580</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3337,6 +3472,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286582</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3434,6 +3574,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286584</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3531,6 +3676,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286586</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3628,6 +3778,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286588</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3725,6 +3880,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287050</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3822,6 +3982,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287051</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3919,6 +4084,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287052</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4016,6 +4186,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287053</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4113,6 +4288,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287054</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4210,6 +4390,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287055</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4315,6 +4500,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287157</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4415,6 +4605,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86288486</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4520,6 +4715,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86288579</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4625,6 +4825,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86288815</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4730,6 +4935,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86288875</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4835,6 +5045,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86289247</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4932,6 +5147,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375193</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5029,6 +5249,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375213</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5126,6 +5351,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375214</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5223,6 +5453,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375220</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5320,6 +5555,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375228</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5417,6 +5657,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375231</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5514,6 +5759,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375235</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5611,6 +5861,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375238</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5708,6 +5963,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375242</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5805,6 +6065,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375243</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5902,6 +6167,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375244</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5999,6 +6269,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375249</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6100,6 +6375,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86386160</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6197,6 +6477,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286565</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6298,6 +6583,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76941637</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6399,6 +6689,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76941701</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6500,6 +6795,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76941715</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6601,6 +6901,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82022172</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6698,6 +7003,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286616</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6795,6 +7105,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286617</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6892,6 +7207,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286618</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6989,6 +7309,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286619</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7086,6 +7411,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286620</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7183,6 +7513,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286621</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7280,6 +7615,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287071</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7377,6 +7717,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375194</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7474,6 +7819,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375208</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7571,6 +7921,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375258</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7668,6 +8023,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375271</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7765,6 +8125,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131257698</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7862,6 +8227,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131259465</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7959,6 +8329,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131260113</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8056,6 +8431,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131260454</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8153,6 +8533,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131260680</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8250,6 +8635,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287063</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8351,6 +8741,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76941623</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8452,6 +8847,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76941679</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8553,6 +8953,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76941719</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8654,6 +9059,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82022082</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8755,6 +9165,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82022114</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8852,6 +9267,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286564</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8949,6 +9369,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287037</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9046,6 +9471,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287038</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9143,6 +9573,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375209</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9240,6 +9675,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375233</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9337,6 +9777,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375241</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9434,6 +9879,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375246</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9531,6 +9981,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375251</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9628,6 +10083,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375269</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9725,6 +10185,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375270</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9822,6 +10287,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375272</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9919,6 +10389,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375274</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10016,6 +10491,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131257647</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10113,6 +10593,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131257750</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10210,6 +10695,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131259760</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10311,6 +10801,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76941658</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10412,6 +10907,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76941730</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10525,6 +11025,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86274503</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10622,6 +11127,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286567</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10719,6 +11229,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286568</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10816,6 +11331,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286569</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10913,6 +11433,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286570</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11010,6 +11535,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286571</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11107,6 +11637,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286572</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11204,6 +11739,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286573</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11301,6 +11841,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286574</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11406,6 +11951,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286824</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11511,6 +12061,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287014</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11608,6 +12163,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287040</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11705,6 +12265,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287041</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11802,6 +12367,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287042</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11899,6 +12469,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287043</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11996,6 +12571,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287044</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12093,6 +12673,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287045</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12191,6 +12776,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287047</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12296,6 +12886,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287121</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12401,6 +12996,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287218</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12506,6 +13106,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287738</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12606,6 +13211,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86288493</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12711,6 +13321,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86288705</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12816,6 +13431,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86288920</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12921,6 +13541,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86289027</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13026,6 +13651,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86289077</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13131,6 +13761,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86289100</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13236,6 +13871,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86289162</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13341,6 +13981,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86289241</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13438,6 +14083,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375199</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13535,6 +14185,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375205</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13632,6 +14287,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375211</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13729,6 +14389,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375216</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13826,6 +14491,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375221</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13923,6 +14593,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375224</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14020,6 +14695,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375256</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14117,6 +14797,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375264</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14218,6 +14903,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86386162</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14319,6 +15009,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86386164</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14420,6 +15115,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76941729</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14533,6 +15233,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86274494</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14630,6 +15335,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286624</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14727,6 +15437,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286625</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14824,6 +15539,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286626</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14921,6 +15641,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286627</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15018,6 +15743,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286628</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15115,6 +15845,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286630</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15212,6 +15947,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286631</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15317,6 +16057,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286862</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15422,6 +16167,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286946</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15519,6 +16269,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287074</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15616,6 +16371,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287075</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15713,6 +16473,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287076</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15810,6 +16575,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287077</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15907,6 +16677,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287078</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16012,6 +16787,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287140</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16117,6 +16897,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287657</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16222,6 +17007,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287729</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16322,6 +17112,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86288514</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16427,6 +17222,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86288982</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16532,6 +17332,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86289172</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16637,6 +17442,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86289237</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16734,6 +17544,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375198</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16831,6 +17646,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375206</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16928,6 +17748,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375217</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17025,6 +17850,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375226</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17122,6 +17952,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375248</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17219,6 +18054,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375252</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17316,6 +18156,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375265</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17417,6 +18262,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86386159</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17518,6 +18368,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86386163</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17619,6 +18474,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86386165</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17720,6 +18580,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86386166</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17817,6 +18682,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286589</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -17922,6 +18792,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286834</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18019,6 +18894,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287058</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18124,6 +19004,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86288932</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18221,6 +19106,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375210</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18322,6 +19212,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86386161</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18419,6 +19314,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286577</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18526,6 +19426,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131260485</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18633,6 +19538,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131260664</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18739,6 +19649,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82022163</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18845,6 +19760,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286566</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18947,6 +19867,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375219</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19049,6 +19974,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375223</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19151,6 +20081,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375230</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19258,6 +20193,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131257765</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19365,6 +20305,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131257828</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19472,6 +20417,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131258022</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19574,6 +20524,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131258105</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19676,6 +20631,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131258210</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19790,6 +20750,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131258260</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19892,6 +20857,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131258518</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -19999,6 +20969,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131258615</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20101,6 +21076,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131258813</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20208,6 +21188,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131258822</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20315,6 +21300,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131258863</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20417,6 +21407,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131259470</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20524,6 +21519,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131259617</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20626,6 +21626,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131259701</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20728,6 +21733,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131259806</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20835,6 +21845,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131259825</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -20937,6 +21952,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131259944</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21039,6 +22059,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131259983</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21141,6 +22166,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131260007</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21248,6 +22278,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131260119</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21350,6 +22385,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131260181</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21452,6 +22492,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131260234</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21559,6 +22604,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131260370</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21661,6 +22711,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131260455</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21768,6 +22823,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131260600</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21875,6 +22935,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131260677</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -21983,6 +23048,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70467064</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22085,6 +23155,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131257444</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22194,6 +23269,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6864745</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22296,6 +23376,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60675815</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22413,6 +23498,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6864741</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22515,6 +23605,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60675814</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22616,6 +23711,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287159</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22713,6 +23813,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287049</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22814,6 +23919,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82022118</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22927,6 +24037,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86274479</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -23024,6 +24139,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286590</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -23121,6 +24241,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286591</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -23226,6 +24351,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287668</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23331,6 +24461,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86288693</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23428,6 +24563,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375196</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23529,6 +24669,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86386157</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23642,6 +24787,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86274510</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23739,6 +24889,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86286594</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23836,6 +24991,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287061</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -23933,6 +25093,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86287062</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -24033,6 +25198,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86288524</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -24138,6 +25308,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86288720</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -24235,6 +25410,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375218</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -24336,8 +25516,251 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86386158</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>